--- a/standardDataset/单轮_有改写.xlsx
+++ b/standardDataset/单轮_有改写.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$169</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -11948,9 +11951,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -12297,3563 +12299,3503 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F169"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2" t="s">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="20" hidden="1" spans="1:6">
+      <c r="A20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2" t="s">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="2" t="s">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="2" t="s">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="2" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="2" t="s">
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2" t="s">
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2" t="s">
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="2" t="s">
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2" t="s">
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="2" t="s">
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="2" t="s">
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="D38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="2" t="s">
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="2" t="s">
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="D40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="2" t="s">
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="D41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="2" t="s">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="D42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="2" t="s">
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="D43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="2" t="s">
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="D44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="2" t="s">
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2" t="s">
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="D46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="2" t="s">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="2" t="s">
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="D48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="2" t="s">
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="2" t="s">
+    </row>
+    <row r="50" hidden="1" spans="1:6">
+      <c r="A50" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="2" t="s">
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="2" t="s">
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="D52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="2" t="s">
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="2" t="s">
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="2" t="s">
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="2" t="s">
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="D56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="2" t="s">
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="D57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="2" t="s">
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="2" t="s">
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="D59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="2" t="s">
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="D60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="2" t="s">
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="D61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="2" t="s">
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="D62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="2" t="s">
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="2" t="s">
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="D64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="2" t="s">
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="D65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="2" t="s">
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="D66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="2" t="s">
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="2" t="s">
+      <c r="D67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="2" t="s">
+    </row>
+    <row r="68" hidden="1" spans="1:6">
+      <c r="A68" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="D68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="2" t="s">
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="D69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2" t="s">
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="2" t="s">
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="2" t="s">
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="D72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="2" t="s">
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="2" t="s">
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="2" t="s">
+      <c r="D74" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="2" t="s">
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="2" t="s">
+      <c r="D75" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="2" t="s">
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="D76" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="2" t="s">
+    </row>
+    <row r="77" hidden="1" spans="1:6">
+      <c r="A77" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="D77" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="2" t="s">
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="2" t="s">
+      <c r="D78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="2" t="s">
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="D79" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="F79" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="2" t="s">
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="D80" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="2" t="s">
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="D81" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="2" t="s">
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="2" t="s">
+      <c r="D82" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="2" t="s">
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="D83" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="2" t="s">
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="D84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="2" t="s">
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="D85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F85" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="2" t="s">
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="2" t="s">
+      <c r="D86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F86" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="2" t="s">
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" s="2" t="s">
+      <c r="D87" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="2" t="s">
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="D88" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F88" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="2" t="s">
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="D89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F89" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="2" t="s">
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="2" t="s">
+      <c r="D90" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="F90" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="2" t="s">
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="2" t="s">
+      <c r="D91" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F91" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="2" t="s">
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="2" t="s">
+      <c r="D92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F92" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="2" t="s">
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="2" t="s">
+      <c r="D93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="F93" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="2" t="s">
+    </row>
+    <row r="94" hidden="1" spans="1:6">
+      <c r="A94" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="2" t="s">
+      <c r="D94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F94" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="2" t="s">
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="2" t="s">
+      <c r="D95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="2" t="s">
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="D96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F96" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="2" t="s">
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="D97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F97" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="2" t="s">
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="D98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F98" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="2" t="s">
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" s="2" t="s">
+      <c r="D99" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="F99" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="2" t="s">
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="2" t="s">
+      <c r="D100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="F100" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="2" t="s">
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="D101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="F101" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="2" t="s">
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="D102" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F102" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="2" t="s">
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="D103" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="F103" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="2" t="s">
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="2" t="s">
+      <c r="D104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="F104" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="2" t="s">
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="2" t="s">
+      <c r="D105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F105" s="2" t="s">
+      <c r="F105" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="2" t="s">
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="2" t="s">
+      <c r="D106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="F106" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="2" t="s">
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="D107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="F107" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="2" t="s">
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="2" t="s">
+      <c r="D108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F108" s="2" t="s">
+      <c r="F108" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="2" t="s">
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="2" t="s">
+      <c r="D109" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="F109" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="2" t="s">
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="2" t="s">
+      <c r="D110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F110" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="2" t="s">
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="2" t="s">
+      <c r="D111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="F111" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="2" t="s">
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="D112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="F112" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="2" t="s">
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="D113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="F113" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="2" t="s">
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="2" t="s">
+      <c r="D114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="F114" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="2" t="s">
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="2" t="s">
+      <c r="D115" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F115" s="2" t="s">
+      <c r="F115" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="2" t="s">
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="2" t="s">
+      <c r="D116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="F116" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="2" t="s">
+    </row>
+    <row r="117" hidden="1" spans="1:6">
+      <c r="A117" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="2" t="s">
+      <c r="D117" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F117" s="2" t="s">
+      <c r="F117" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="2" t="s">
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="2" t="s">
+      <c r="D118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="F118" s="2" t="s">
+      <c r="F118" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="2" t="s">
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="D119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="F119" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="2" t="s">
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="2" t="s">
+      <c r="D120" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="F120" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="2" t="s">
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="2" t="s">
+      <c r="D121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="F121" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="2" t="s">
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="2" t="s">
+      <c r="D122" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="F122" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="2" t="s">
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="D123" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="F123" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" s="2" t="s">
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="2" t="s">
+      <c r="D124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F124" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" s="2" t="s">
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="D125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F125" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" s="2" t="s">
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="2" t="s">
+      <c r="D126" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F126" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" s="2" t="s">
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="2" t="s">
+      <c r="D127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F127" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="2" t="s">
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="2" t="s">
+      <c r="D128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F128" s="2" t="s">
+      <c r="F128" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" s="2" t="s">
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="D129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="F129" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" s="2" t="s">
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="2" t="s">
+      <c r="D130" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F130" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="2" t="s">
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="2" t="s">
+      <c r="D131" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F131" s="2" t="s">
+      <c r="F131" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" s="2" t="s">
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="2" t="s">
+      <c r="D132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="F132" s="2" t="s">
+      <c r="F132" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" s="2" t="s">
+    </row>
+    <row r="133" hidden="1" spans="1:6">
+      <c r="A133" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="D133" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F133" s="2" t="s">
+      <c r="F133" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" s="2" t="s">
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="D134" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="F134" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" s="2" t="s">
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="D135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="F135" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" s="2" t="s">
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" s="2" t="s">
+      <c r="D136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="F136" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" s="2" t="s">
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="2" t="s">
+      <c r="D137" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="F137" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" s="2" t="s">
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D138" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" s="2" t="s">
+      <c r="D138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="F138" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" s="2" t="s">
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="D139" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="F139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" s="2" t="s">
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="2" t="s">
+      <c r="D140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="F140" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" s="2" t="s">
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="2" t="s">
+      <c r="D141" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F141" s="2" t="s">
+      <c r="F141" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" s="2" t="s">
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="D142" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="F142" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" s="2" t="s">
+    </row>
+    <row r="143" hidden="1" spans="1:6">
+      <c r="A143" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" s="2" t="s">
+      <c r="D143" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F143" s="2" t="s">
+      <c r="F143" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" s="2" t="s">
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" s="2" t="s">
+      <c r="D144" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="F144" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" s="2" t="s">
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D145" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="2" t="s">
+      <c r="D145" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F145" s="2" t="s">
+      <c r="F145" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" s="2" t="s">
+    </row>
+    <row r="146" hidden="1" spans="1:6">
+      <c r="A146" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="2" t="s">
+      <c r="D146" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="F146" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" s="2" t="s">
+    </row>
+    <row r="147" hidden="1" spans="1:6">
+      <c r="A147" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="D147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="F147" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" s="2" t="s">
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="2" t="s">
+      <c r="D148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F148" s="2" t="s">
+      <c r="F148" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" s="2" t="s">
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="D149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="F149" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" s="2" t="s">
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" s="2" t="s">
+      <c r="D150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="F150" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" s="2" t="s">
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="F151" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" s="2" t="s">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="D152" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="F152" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" s="2" t="s">
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="2" t="s">
+      <c r="D153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="F153" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" s="2" t="s">
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="2" t="s">
+      <c r="D154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F154" s="2" t="s">
+      <c r="F154" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" s="2" t="s">
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="2" t="s">
+      <c r="D155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F155" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" s="2" t="s">
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="2" t="s">
+      <c r="D156" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F156" s="2" t="s">
+      <c r="F156" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="2" t="s">
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="2" t="s">
+      <c r="D157" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="F157" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" s="2" t="s">
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="2" t="s">
+      <c r="D158" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F158" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" s="2" t="s">
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" s="2" t="s">
+      <c r="D159" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="F159" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" s="2" t="s">
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="2" t="s">
+      <c r="D160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F160" s="2" t="s">
+      <c r="F160" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" s="2" t="s">
+    </row>
+    <row r="161" hidden="1" spans="1:6">
+      <c r="A161" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" s="2" t="s">
+      <c r="D161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F161" s="2" t="s">
+      <c r="F161" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" s="2" t="s">
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="2" t="s">
+      <c r="D162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F162" s="2" t="s">
+      <c r="F162" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" s="2" t="s">
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" s="2" t="s">
+      <c r="D163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F163" s="2" t="s">
+      <c r="F163" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" s="2" t="s">
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164" s="2" t="s">
+      <c r="D164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F164" s="2" t="s">
+      <c r="F164" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" s="2" t="s">
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D165" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" s="2" t="s">
+      <c r="D165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F165" s="2" t="s">
+      <c r="F165" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" s="2" t="s">
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D166" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="2" t="s">
+      <c r="D166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F166" s="2" t="s">
+      <c r="F166" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" s="2" t="s">
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="D167" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="2" t="s">
+      <c r="D167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F167" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" s="2" t="s">
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" s="2" t="s">
+      <c r="D168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F168" s="2" t="s">
+      <c r="F168" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" s="2" t="s">
+    </row>
+    <row r="169" hidden="1" spans="1:6">
+      <c r="A169" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="2" t="s">
+      <c r="D169" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F169" s="2" t="s">
+      <c r="F169" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G169" s="2"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C169" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="好的!关于如何登录预数系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问系统地址**  &#10;   打开谷歌浏览器（Chrome），在地址栏输入以下网址并访问：  &#10;   `https://jyys.zy.com/jyys/admin/login`&#10;&#10;2. **输入账号密码**  &#10;   使用您的**员工通行证**作为账号和密码进行登录。&#10;&#10;3. **找回密码（如需要）**  &#10;   如果您修改过密码但忘记了，请点击以下链接进行找回：  &#10;   `https://ucin.zy.com/forgot_password`&#10;&#10;**💡 提示**: &#10;- 该系统仅支持**谷歌浏览器**，建议使用该浏览器以确保功能正常。&#10;- 登录时请确保网络连接稳定。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Windows安装零信任，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并准备安装包**  &#10;   访问以下链接下载最新版本的Windows零信任工具：  &#10;   https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  &#10;   &gt; 若电脑已安装“安全助手”，建议先卸载（见下方提示），再安装零信任；若无安全助手，可直接覆盖安装。&#10;&#10;2. **运行安装程序**  &#10;   双击下载的 `.exe` 文件，弹出用户账户控制窗口时点击 **“是”**。&#10;&#10;3. **同意许可协议**  &#10;   在安装向导中点击 **“我同意”** 继续。&#10;&#10;4. **选择安装位置**  &#10;   可自定义安装路径，一般保持默认即可，点击 **“安装”** 开始安装。&#10;&#10;5. **等待安装完成**  &#10;   安装完成后，默认会勾选“运行零信任”，此时桌面会出现“零信任”图标。&#10;&#10;6. **扫码登录使用**  &#10;   打开桌面上的“零信任”客户端，使用企业微信或指定方式扫码登录。  &#10;   &gt; 若首次安装提示需输入控制器地址，请输入：`sec.zy.com` 或 `124.71.208.207`，确认后扫码登录。&#10;&#10;**💡 提示**:  &#10;- 管理员口令和安全助手卸载码均为：`e2vPsv8$`  &#10;- 若安装后未显示“零信任”图标，可能是与IOA软件冲突，可尝试手动运行：`C:\Program Files (x86)\TrustCyberLink\TrustCyberLink.exe`  &#10;- 登录零信任后请勿退出客户端，否则无法访问内部系统（如TMS、EVIP等）  &#10;- 如遇浏览器访问问题（如403错误），建议更换为Google或Firefox浏览器，并刷新策略&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在电脑上安装打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备阶段：收集信息并下载驱动**&#10;   - 确认打印机的**IP地址**和**型号**（部分共用打印机需准备部门密码）。&#10;   - 根据电脑系统下载对应的驱动包：&#10;     - **Windows系统**：访问京瓷打印机驱动下载页面，将驱动包保存到电脑硬盘。&#10;     - **Mac系统**：访问京瓷打印机Mac系统驱动下载页面，下载驱动包。&#10;&#10;2. **Windows系统安装步骤**&#10;   - **解压与启动**：解压下载的驱动包，进入文件夹双击 `Setup.exe` 运行安装程序。&#10;   - **自定义安装**：接受协议，选择“自定义安装”。&#10;   - **配置信息**：根据实际打印机的型号和IP地址填写相关信息，添加打印机驱动及升级组件。&#10;   - **完成安装**：等待安装完成。&#10;&#10;3. **Mac系统安装步骤**&#10;   - **运行安装程序**：双击下载的驱动包。若桌面未找到，可使用 `Command + 空格键` 搜索框输入 `Kyocera OS X 10.9+ Web build 2024.05.16` 查找并打开。&#10;   - **执行安装**：一路点击安装直至完成。&#10;   - **重启电脑**：安装完成后，**必须重启电脑**才能生效。&#10;&#10;4. **添加打印机设备**&#10;   - **Windows**：打开控制面板 -&gt; 硬件和设备 -&gt; 设备和打印机，右键属性进行名称修改或设置双面打印。&#10;   - **Mac**：进入“系统偏好设置” -&gt; “打印机与扫描仪” -&gt; 点击“添加设置”，选择“IP连接”，输入打印机IP地址并选择对应协议，完成添加。&#10;&#10;5. **后续设置（可选）**&#10;   - **取消脱机状态**：若打印机显示脱机，需在设置中取消SNMP状态检查。&#10;   - **添加部门ID**：如需使用部门代码，请在打印机属性或专用应用程序中添加部门ID。&#10;&#10;**💡 提示**: &#10;- 安装前请务必确认网络通畅，网线连接正常。&#10;- Mac用户安装驱动后务必重启电脑。&#10;- 如遇到“程序已暂停”问题，可前往控制面板的“设备和打印机”中，双击打印机图标，取消“暂停打印”前的勾选。&#10;- 如有其他问题，可联系IT帮助台或在OA系统 (http://oa.zy.com) 上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于苹果电脑（Mac）零信任加载不出来的问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并添加系统权限**  &#10;   如果打开零信任时提示需要输入密码提权，或密码提示不对，通常是因为macOS未给予SDP客户端足够权限。  &#10;   - 打开 **系统设置** &gt; **隐私与安全性**。  &#10;   - 找到 **零信任** 程序，开启其相关的 SDP 权限（如完全磁盘访问权限、屏幕录制等）。  &#10;   - 若之前密码错误，请检查密码中是否包含特殊字符串，修改后重新尝试登录。&#10;&#10;2. **修复进程文件损坏**  &#10;   如果零信任无法启动或闪退，可能是 `sdp_engine` 进程文件损坏。  &#10;   - 下载修复文件：[sdp_engine.exe](https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe)  &#10;   - 将下载的文件复制到零信任安装目录进行替换。  &#10;     *注：Mac版路径可能不同，通常位于应用程序包内，若不确定可尝试重启客户端或联系管理员获取Mac专用修复包。*&#10;&#10;3. **处理IOA冲突**  &#10;   如果安装后不显示“零信任”图标或无法加载，可能是与旧版IOA软件冲突。  &#10;   - 确认电脑上是否安装了IOA软件，如有建议卸载。  &#10;   - 卸载后，退出零信任客户端，重新扫码登录。&#10;&#10;4. **解决JavaScript错误或启动失败**  &#10;   如果启动时提示“JavaScript错误”无法正常启动：  &#10;   - 打开 **终端** (Terminal)。  &#10;   - 输入命令：`sudo vi /etc/hosts`  &#10;   - 在文件中添加一行：`127.0.0.1 localhost`  &#10;   - 保存退出后，重新启动零信任客户端。&#10;&#10;5. **切换控制器地址**  &#10;   如果提示“连接控制器失败”：  &#10;   - 在零信任界面选择 **控制器切换**。  &#10;   - 手动输入地址：`124.71.208.207` 或 `sec.zy.com`。  &#10;   - 若仍无效，尝试重置控制器配置后再次输入上述地址。&#10;&#10;6. **清理第三方干扰**  &#10;   如果运行缓慢或杀毒软件弹窗导致加载失败：  &#10;   - 暂时卸载或禁用第三方杀毒软件（如360、火绒等，虽然这些多为Windows软件，但Mac上若有类似安全工具也需检查）。  &#10;   - 禁用不必要的开机启动项。&#10;&#10;**💡 提示**: &#10;- 操作前请确保网络连接正常。&#10;- 如果是企业环境，部分权限配置可能需要联系IT管理员协助。&#10;- 若以上步骤均无效，建议完全卸载零信任客户端后，重新下载安装最新版本。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**解决账号无权限查看回放**的问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认当前登录账号**&#10;   检查您目前使用的监控客户端（iVMS-4200）或网页端登录的账号。&#10;   - 如果您使用的是 `user` (密码: `345110jk`)，该账号为**普通用户2**，系统设定为**无回放功能**。&#10;   - 如果您需要查看回放，必须切换到拥有回放权限的账号。&#10;&#10;2. **切换至有回放功能的账号**&#10;   根据您使用的平台，执行以下对应操作：&#10;   &#10;   *场景A：使用 iVMS-4200 监控客户端*&#10;   - 打开“iVMS-4200”客户端，进入主菜单界面右侧的【设备管理】。&#10;   - 找到您需要查看的设备，点击旁边的**笔形状图标**（编辑按钮）。&#10;   - 在弹出的窗口中，将用户名修改为 `userxq`，密码修改为 `345110xq`。&#10;   - 保存后，等待状态显示为&quot;**在线**&quot;，即表示连接成功且已切换至有回放权限的账号。&#10;&#10;   *场景B：使用 Edge 浏览器查看监控*&#10;   - 直接退出当前登录，重新输入有回放功能的账号信息：&#10;     - 用户名：`userxq`&#10;     - 密码：`345110xq`&#10;   - 首次使用可能会提示下载插件，请根据提示完成下载。&#10;   - 若页面显示异常，请点击左上角【e】标志，开启兼容性模式或在IE模式下打开。&#10;&#10;3. **验证回放功能**&#10;   切换账号成功后，尝试进入【远程回放】或【查看回放】界面，此时应能正常调取录像。&#10;&#10;**💡 提示**: &#10;- 账号 `user` 仅具备实时监控权限，无法进行历史录像回放；只有账号 `userxq` 才具备完整的回放功能。&#10;- 如果切换账号后仍无法查看，请检查网络连接是否正常，或联系IT帮助台/在OA系统（http://oa.zy.com）上填写报障单寻求进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于安装打印机驱动，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认系统类型并下载驱动**&#10;   - **Windows 用户**：访问“京瓷打印机驱动下载”页面，将驱动包下载到电脑硬盘。&#10;   - **Mac 用户**：访问“京瓷打印机mac系统驱动下载”页面，下载对应的驱动包。&#10;   - *注：如果是理光、富士施乐或佳能品牌，请前往对应品牌的官方支持页面下载（如理光 MPC5503/MP6054，富士施乐 P288/M288，佳能 MF244/MF249）。*&#10;&#10;2. **准备打印机信息**&#10;   - 在安装前，请先查询并记录打印机的 **IP地址** 和 **型号**。&#10;   - 如果是部门共用打印机，请提前准备好 **部门密码**。&#10;&#10;3. **执行安装程序**&#10;   - **Windows 系统**：&#10;     1. 解压下载的驱动包。&#10;     2. 进入文件夹，双击 `Setup.exe` 运行安装程序。&#10;     3. 接受协议，选择“自定义安装”。&#10;     4. 根据实际型号和 IP 地址填写相关信息，完成驱动及组件安装。&#10;   - **Mac 系统**：&#10;     1. 双击下载的驱动包。&#10;     2. 若桌面未显示，按 `Command + 空格键` 搜索 &quot;Kyocera OS X 10.9+ Web build 2024.05.16&quot; 并打开。&#10;     3. 一路点击完成安装。&#10;     4. **重要**：安装完成后，必须**重启电脑**。&#10;&#10;4. **添加打印机设备**&#10;   - **Windows**：安装完成后，通常会自动识别；若需手动设置，可进入控制面板 &gt; 硬件和设备 &gt; 打印机属性进行配置。&#10;   - **Mac**：&#10;     1. 进入“系统偏好设置” &gt; “打印机与扫描仪”。&#10;     2. 点击“添加设置”，选择“IP连接”。&#10;     3. 输入之前记录的打印机 IP 地址，选择正确的连接协议。&#10;     4. 完成添加后即可使用。&#10;&#10;5. **特殊配置（如需）**&#10;   - **设置部门ID**（Mac）：打开“应用程序”中的打印机程序，选择对应 IP 的打印机，在界面中添加部门 ID。&#10;   - **解决脱机问题**（Windows）：若打印机显示脱机，需在属性中取消勾选 SNMP 状态检测。&#10;&#10;**💡 提示**: &#10;- 安装过程中若遇到网络无法识别打印机型号，请检查打印机网线是否松动或网络连接是否正常。&#10;- 如遇其他问题，可联系 IT 帮助台或在 OA 系统 (http://oa.zy.com) 上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载Windows Seafile安装包,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问下载页面**  &#10;   打开浏览器，访问 Seafile 官方下载地址：https://www.seafile.com/download/&#10;&#10;2. **选择客户端类型**  &#10;   在页面中找到并点击 **“seafile 桌面客户端下载”** 选项。&#10;&#10;3. **开始下载安装包**  &#10;   系统会自动识别您的操作系统（Windows），点击下载按钮即可获取 Windows 版本的安装包。&#10;&#10;4. **运行安装程序**  &#10;   下载完成后，双击安装包进行安装。若弹出安全提示，请根据指引确认继续安装。&#10;&#10;**💡 提示**: &#10;- 安装时建议**不要选择C盘**作为资料保存路径，尽量选择空间较大的磁盘分区。&#10;- 登录时需填写部门云盘网站地址、邮箱及OA密码。&#10;- 如遇其他问题，可联系IT帮助台或在OA上提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载希沃传屏发送端Windows安装包,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问希沃官网**  &#10;   打开浏览器，在地址栏输入 `www.baidu.com`，在搜索框中输入“希沃官网”，点击进入官方网站（请认准官方链接，避免进入错误页面）。&#10;&#10;2. **定位软件下载入口**  &#10;   在官网首页点击【服务支持】菜单，选择【希沃软件】。向下滚动页面，找到【希象传屏】栏目，点击【立即下载】。&#10;&#10;3. **选择并下载对应版本**  &#10;   在跳转后的页面中，再次找到【希象传屏】。根据您的设备需求进行选择：&#10;   - **发送端**：请选择 **Windows版本** 进行下载（适用于您的电脑系统）。&#10;   - *注：接收端通常指希沃一体机，需选择Windows版本；若您在其他电脑上使用发送功能，也请选择Windows版。*&#10;&#10;4. **安装软件**  &#10;   下载完成后，双击安装包进行安装。如果C盘空间不足，可在安装过程中选择其他磁盘分区进行安装。&#10;&#10;**💡 提示**: &#10;- 投屏前请确保发送端电脑与接收端（一体机）连接在**同一个Wi-Fi网络**下。&#10;- 如在使用过程中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于连接打印机,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备阶段：获取必要信息**&#10;   - 查看打印机机身标签或屏幕，记录**打印机IP地址**和**打印机型号**。&#10;   - 如果是共用打印机，请提前准备好对应的**部门密码/ID**。&#10;&#10;2. **MAC系统用户操作指引**&#10;   - **下载驱动**：访问京瓷官网下载Mac系统驱动包。&#10;   - **安装驱动**：双击驱动包进行安装（若桌面未找到，可使用 `Command + 空格` 搜索 &quot;Kyocera OS X 10.9+ Web build 2024.05.16&quot; 并打开）。&#10;   - **重启电脑**：驱动安装完成后，**必须重启电脑**才能生效。&#10;   - **添加打印机**：&#10;     1. 进入“系统偏好设置” &gt; “打印机与扫描仪”。&#10;     2. 点击“添加设置”，选择“IP连接”。&#10;     3. 输入之前记录的**IP地址**，选择对应的连接协议。&#10;     4. 完成添加后即可打印。&#10;&#10;3. **Windows系统用户操作指引**&#10;   - **下载并解压驱动**：从官网下载驱动包并保存到硬盘，右键解压。&#10;   - **运行安装程序**：&#10;     1. 进入文件夹，双击 `Setup.exe`。&#10;     2. 接受协议，选择“自定义安装”。&#10;     3. 根据实际**打印机型号**和**IP地址**填写信息，完成驱动及组件安装。&#10;   - **配置打印机属性**：&#10;     1. 打开“控制面板” &gt; “硬件和设备” &gt; “设备和打印机”。&#10;     2. 右键点击新安装的打印机，选择“打印机属性”。&#10;     3. **修改名称**：在常规选项卡中修改为易识别的名称。&#10;     4. **设置双面打印**：在相关选项中开启。&#10;     5. **处理脱机状态**：若显示脱机，需在端口设置中取消勾选“SNMP状态启用”。&#10;     6. **添加部门ID**：进入“设备设置” &gt; “管理员”，输入对应的部门ID（每机每部门ID不同）。&#10;&#10;**💡 提示**: &#10;- 如果电脑无法自动识别打印机型号，请检查打印机网线是否松动或网络是否正常。&#10;- 遇到非软件问题（如卡纸、硒鼓故障、无法开机等），请直接联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**连接校区共享文件夹**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认账号密码规则**&#10;   - **老师电脑**：&#10;     - **用户名**：根据业务类型填写（成长-班辅用 `fdb`，亲子-个辅用 `gf`，志业用 `sgz`）。&#10;     - **密码**：格式为 `zy` + `校区名称` + `业务缩写`。&#10;       *例如：鸟巢成长校区，用户名为 `fdb`，密码为 `zyncfdb`。*&#10;   - **课室一体机**：&#10;     - **用户名**：`ks`&#10;     - **密码**：`ks`&#10;     *注意：ks 文件夹通常只有读取权限。*&#10;&#10;2. **Windows 系统连接方法**&#10;   - 打开【此电脑】或任意文件夹。&#10;   - 在地址栏输入共享地址：`\\192.168.0.26`，按回车键。&#10;   - 在弹出的安全验证窗口中，输入上述对应的**用户名**和**密码**。&#10;   - **重要**：勾选“记住我的凭据”，点击确认。&#10;   - 双击需要访问的共享文件夹即可使用。&#10;   - *(可选)* 如需桌面快捷方式：右键点击该文件夹，选择【创建快捷方式】，将其移动到桌面。&#10;&#10;3. **Mac (MAC) 系统连接方法**&#10;   - 打开 Finder（访达），点击顶部菜单栏的【前往】&gt;【连接服务器】（或直接按快捷键 `Command + K`）。&#10;   - 在服务器地址栏输入：`smb://192.168.0.26`。&#10;   - 点击连接，在弹出的窗口中选择注册用户并输入**用户名**和**密码**。&#10;   - 勾选“记住密码”后点击确认，共享盘将自动挂载。&#10;   - *(可选)* 设置开机自动挂载：进入【系统偏好设置】&gt;【用户与群组】&gt;【登录项】，将已挂载的网络驱动器图标拖入列表中。&#10;&#10;4. **常见问题处理**&#10;   - **无法连接/提示多连接**：尝试注销或重启电脑。&#10;   - **凭证错误**：按 `Win + R` 输入 `control` 打开控制面板，进入【凭据管理器】&gt;【Windows 凭据】，找到 `192.168.0.26` 并删除，重启电脑后重新连接。&#10;&#10;**💡 提示**: &#10;- 如果操作中遇到其他问题，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）上填写 IT 报障单。&#10;- 确保输入的校区名称和业务缩写准确无误，否则会导致密码错误。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Windows系统安装京瓷打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备阶段：下载驱动与收集信息**&#10;   - 访问京瓷打印机驱动下载页面，将驱动包下载到电脑硬盘。&#10;   - 提前确认打印机的**IP地址**和**型号**（部分共用打印机还需准备部门密码）。&#10;&#10;2. **解压并启动安装程序**&#10;   - 解压下载的驱动包文件夹。&#10;   - 进入文件夹，双击运行 `Setup.exe` 启动安装向导。&#10;&#10;3. **执行自定义安装**&#10;   - 在安装界面点击“接受”协议。&#10;   - 选择“自定义安装”模式。&#10;   - 根据实际打印机的**型号**和**IP地址**填写相关信息。&#10;   - 勾选需要添加的打印机驱动及升级组件，按提示完成安装。&#10;&#10;4. **配置打印机属性**&#10;   - 打开“控制面板”，进入“硬件和设备”（或“设备和打印机”）。&#10;   - 右键点击新安装的打印机，选择“打印机属性”。&#10;   - **修改名称**：将打印机名称修改为易于识别的名字。&#10;   - **设置双面打印**：在属性中开启双面打印功能。&#10;   - **处理脱机状态**：若打印机显示“脱机”，需在设置中取消“SNMP 状态检测”。&#10;   - **添加部门ID**：如需使用部门计费，请在设备设置中添加对应的部门ID。&#10;&#10;**💡 提示**: &#10;- 安装前务必确认打印机IP地址正确，否则可能导致连接失败。&#10;- 如果打印机显示脱机，通常是因为启用了SNMP状态检测，请记得在端口设置中将其取消。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决控制器连接失败问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，在设置或连接选项中，手动将控制器地址切换为 `124.71.208.207`。&#10;&#10;2. **重置并重新输入控制器地址**  &#10;   如果切换地址后问题依然存在：&#10;   - 选择“重置控制器”选项；&#10;   - 重置完成后，再次手动输入控制器地址 `124.71.208.207` 进行连接。&#10;&#10;**💡 提示**: 请确保网络连接正常，且防火墙未拦截相关端口。如仍无法解决，建议联系IT帮助台获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于清理C盘空间,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带磁盘清理工具**  &#10;   按下键盘上的 `Win` 键，搜索并打开“磁盘清理”工具，选择 C 盘进行扫描和清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   - 打开微信，点击左下角菜单进入“设置”。&#10;   - 选择“文件管理”，点击“打开文件夹”。&#10;   - 在弹出的窗口中点击“更改”，将存储路径修改为 C 盘以外的其他盘符（如 D 盘或 E 盘）。&#10;   - 更改完成后，微信会自动迁移数据，释放大量 C 盘空间。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   - 打开企业微信，进入“设置”。&#10;   - 选择“存储管理”，按照提示将文件存储位置更改至非 C 盘分区。&#10;&#10;4. **手动删除临时文件**  &#10;   - 按下 `Win + R` 键，输入 `%temp%` 并回车。&#10;   - 在打开的文件夹中全选所有文件（Ctrl + A），然后删除（Shift + Delete 可彻底删除）。&#10;   - *注意：部分正在使用的文件可能无法删除，跳过即可。*&#10;&#10;5. **深度清理微信缓存文件（可选）**  &#10;   - 登录微信后，依次点击“设置” &gt; “文件管理” &gt; “打开文件夹”。&#10;   - 进入 `FileStorage` 文件夹，根据需求选择性删除以下子文件夹中的内容：&#10;     - **Cache**：缓存文件，可按月份删除。&#10;     - **Files**：接收的文件（Word、Excel、PDF等），建议确认后再删除。&#10;     - **Image**：聊天表情和图片，加密处理，删除需谨慎。&#10;     - **Video**：视频文件及封面，占用空间较大，建议优先清理。&#10;   - *警告：删除后无法恢复，请谨慎操作。*&#10;&#10;**💡 提示**: &#10;- 在进行任何大文件迁移或删除操作前，建议先备份重要数据。&#10;- 如果 C 盘空间已满导致程序运行异常（如报错“程序文件缺失”），请先执行上述清理步骤腾出空间，再进行后续操作。&#10;- 如遇安全软件误报，请点击“允许”；若问题仍未解决，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）上提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于绑定邮箱手机号，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **新用户首次登录绑定**  &#10;   如果您是第一次使用263邮箱，必须在电脑网页端完成绑定：&#10;   - 打开浏览器访问：https://www.263.net/&#10;   - 点击【登录】，输入您的【邮箱账号】和【密码】（若忘记密码可点击“忘记密码”重置）。&#10;   - 在验证环节输入【手机号码】和收到的【短信验证码】。&#10;   - 提示“手机号验证成功”即表示绑定完成。&#10;&#10;2. **更换或重新绑定手机号（旧手机可用）**  &#10;   如果您需要更换绑定的手机号，且旧手机号仍能接收短信：&#10;   - 登录邮箱网页版，点击右上角【账户】头像，选择【设置】。&#10;   - 进入【账户信息】，点击【点击这里绑定手机】。&#10;   - 先点击【解除绑定】，获取并输入旧手机的验证码确认解绑。&#10;   - 解绑成功后，点击【绑定】，输入新的【手机号码】和【验证码】，点击确定即可完成新号码绑定。&#10;&#10;3. **更换或重新绑定手机号（旧手机已注销/无法接收短信）**  &#10;   如果旧手机号已注销或无法接收验证码，需通过OA系统申请变更：&#10;   - 登录OA系统，点击【发起流程】。&#10;   - 选择路径：【IT类】-【IT服务】-【账户/权限申请】。&#10;   - 在“系统”中选择&quot;263企业邮箱”，在“描述”中清楚写明您的需求（例如：原手机号已注销，需更换绑定新手机号）。&#10;   - 提交后等待IT部门处理。&#10;&#10;4. **手机端App绑定提示**  &#10;   如果您在手机App登录时提示“绑定的手机号码已经变更”：&#10;   - 请先登录网页端邮箱 (mail.zy.com)。&#10;   - 点击右上角头像 -&gt; 【设置】 -&gt; 【账户信息】 -&gt; 【手机号码】。&#10;   - 点击【更改】，输入新手机号及验证码保存即可。&#10;&#10;**💡 提示**: &#10;- 绑定手机号是安全验证的重要环节，请务必确保填写的手机号能正常接收短信。&#10;- 若遇到收不到验证码、IP被限制等异常情况，请通过OA系统提交【IT报障/预约服务单】寻求协助。"/>
+        <filter val="好的!关于更换邮箱绑定的手机号，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **场景一：旧手机号仍能接收短信验证码**&#10;   若您的旧手机号依然可用，可直接在网页端自行解绑并重新绑定：&#10;   - 登录电脑浏览器访问 `https://www.263.net/`。&#10;   - 输入邮箱账号和密码登录（若忘记密码需先重置）。&#10;   - 点击右上角【账户】头像，选择【设置】。&#10;   - 点击【账户信息】下的【点击这里绑定手机】。&#10;   - 点击【解除绑定】，输入旧手机收到的验证码后确认解绑。&#10;   - 点击【绑定】，输入新手机号码及收到的短信验证码，点击确定即可完成换绑。&#10;&#10;2. **场景二：旧手机号已注销或无法接收短信**&#10;   若旧手机号无法使用，需通过OA系统发起流程申请变更：&#10;   - 登录OA系统，点击【发起流程】。&#10;   - 依次选择【IT类】-【IT服务】-【账户/权限申请】。&#10;   - 在“系统”选项中选择&quot;263企业邮箱”。&#10;   - 在“描述”栏中清晰填写您的需求（例如：原手机号已注销，申请更换为新手机号XXX）。&#10;   - 提交流程等待IT部门处理。&#10;&#10;3. **场景三：在手机APP端发现手机号异常**&#10;   若在263企业邮箱APP登录时提示“绑定的手机号码已经变更”：&#10;   - 请使用电脑浏览器访问 `mail.zy.com` 登录邮箱。&#10;   - 按照上述“场景一”的步骤，在网页端完成手机号的更改和保存。&#10;&#10;**💡 提示**: &#10;- 首次登录263邮箱必须关联手机号码。&#10;- 如果更换手机号过程中遇到其他问题，可联系IT帮助台或在OA上填写IT报障单（地址：http://oa.zy.com）。&#10;- 修改密码后，如需在企业微信中使用邮箱，需重新进行绑定操作。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何调整绩效计划，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认当前状态**  &#10;   首先查看您的绩效计划是否已经提交审批：&#10;   - **情况一：未提交审批**  &#10;     您可以直接在系统中修改目标内容，修改完成后重新提交即可。&#10;   - **情况二：已提交审批**  &#10;     需要先将目标撤回，才能进行修改。&#10;&#10;2. **执行撤回与修改（针对已提交的情况）**  &#10;   - 登录企业门户（推荐使用谷歌Chrome浏览器），访问绩效系统。&#10;   - 在首页点击「我的待办」或右上角的待办图标，找到对应的绩效计划任务。&#10;   - 点击“去处理”进入目标制定界面。&#10;   - 选择“撤回目标”功能。&#10;   - **注意**：成功撤回后，您的直接上级会收到通知（提示：“绩效君的2025年年度目标已经撤回调整，请知晓”）。&#10;   - 撤回成功后，您即可重新编辑并修改绩效目标。&#10;&#10;3. **特殊情况处理（岗位调动）**  &#10;   如果您或团队成员在年中发生了岗位调动，且需要调整绩效计划：&#10;   - **方式A**：由员工本人按上述步骤撤回目标后进行修改。&#10;   - **方式B**：由现直接上级对原绩效计划进行“驳回”，然后由员工修订。&#10;   - **重要提醒**：新制定的绩效目标必须完成**目标审批**流程后，方可进行年中或年末评估。&#10;&#10;4. **新入职员工特别指引**  &#10;   如果是刚转正的新伙伴需要制定年度绩效计划，建议直接咨询HRBP领取具体的操作指引文件。&#10;&#10;**💡 提示**: &#10;- 无论哪种修改方式，请务必确保修改后的目标完成了**审批流程**，否则无法参与后续的绩效评估。&#10;- 建议在修改前与您的直接上级沟通确认，以免因频繁撤回影响审批效率。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重置邮箱密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开企业微信**  &#10;   登录您的企业微信账号。&#10;&#10;2. **进入IT服务台**  &#10;   点击底部菜单栏的【工作台】，在应用列表中找到并点击【IT服务台】。&#10;&#10;3. **选择密码重置功能**  &#10;   在IT服务台页面中，点击【更多功能】，然后选择【邮箱密码重置】。&#10;&#10;4. **按提示完成重置**  &#10;   根据页面显示的步骤指引，输入相关信息并完成密码修改。&#10;&#10;5. **重新绑定（如需要）**  &#10;   如果您之前将263邮箱与企业微信进行了绑定，重置密码后需重新登录企业微信-【工作台】-【263企业邮箱】，输入新密码以完成重新绑定，确保正常使用。&#10;&#10;**💡 提示**: &#10;- 如果在使用过程中遇到其他问题，可联系IT帮助台或在OA系统上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;- 若因旧手机号无法接收验证码导致无法重置，需在OA系统发起“账户/权限申请”流程进行手机号变更。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**解决用户名不合法问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **返回上一级菜单**  &#10;   在零信任客户端登录界面，点击“返回”或“上一级”按钮，退出当前的输入状态。&#10;&#10;2. **选择快捷方式登录**  &#10;   不要手动输入用户名，直接选择界面上的&quot;**快捷方式登录**&quot;（或类似“扫码登录”、“免密登录”）选项。&#10;&#10;3. **重新进行认证**  &#10;   根据提示使用手机扫码或其他方式完成身份验证，即可正常进入系统。&#10;&#10;**💡 提示**: &#10;*   此方法同样适用于提示“会话已经过期”或“扫码登录认证失败”的情况。&#10;*   如果之前尝试过输入用户名导致报错，请务必先清除输入框内容再执行上述步骤。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于查看监控回放权限，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认账号权限类型**  &#10;   监控系统区分了“有回放功能”和“无回放功能”的两种普通用户账号。要查看回放，必须使用具备回放权限的账号：&#10;   - ✅ **有回放功能账号**：用户名 `userxq`，密码 `345110xq`&#10;   - ❌ **无回放功能账号**：用户名 `user`，密码 `345110jk`（此账号无法查看回放）&#10;&#10;2. **在客户端中切换或修改账号**  &#10;   如果您当前使用的是无回放功能的账号，请按以下步骤切换：&#10;   - 打开监控客户端 **&quot;iVMS-4200&quot;**。&#10;   - 在主菜单界面右侧找到 **“设备管理”**。&#10;   - 选择需要更改的监控设备，点击 **“笔形状图标”**（编辑按钮）。&#10;   - 将账号修改为上述 **有回放功能的账号** (`userxq` / `345110xq`)。&#10;   - 保存后，等待状态显示为 **“在线”**，即表示连接成功且拥有回放权限。&#10;&#10;3. **执行远程回放操作**  &#10;   账号切换成功后，进入主预览界面，即可进行 **“远程回放”** 操作查看历史录像。&#10;&#10;**💡 提示**: &#10;- 登录软件时使用的账号并非监控回放账号，请务必区分清楚。&#10;- 如果是在 Edge 浏览器查看监控，首次使用需下载插件，并开启兼容性模式（左上角【e】标志），同样需使用 `userxq` 账号才能查看回放。&#10;- 如操作中遇到其他问题，可联系 IT 帮助台或在 OA 系统 (http://oa.zy.com) 上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Windows上安装京瓷打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备信息与下载驱动**  &#10;   在安装前，请先确认打印机的**IP地址**和**型号**（部分共用打印机需准备部门密码）。  &#10;   访问“京瓷打印机驱动下载”页面，将驱动包下载并保存到电脑硬盘中。&#10;&#10;2. **解压与启动安装程序**  &#10;   找到下载的驱动包进行**解压**。  &#10;   进入文件夹，双击运行 **Setup.exe** 文件启动安装向导。&#10;&#10;3. **执行自定义安装**  &#10;   点击“接受”协议，选择 **“自定义安装”** 模式。  &#10;   根据实际打印机的**型号**和**IP地址**填写相关信息。  &#10;   勾选需要添加的打印机驱动及升级组件，按提示完成安装。&#10;&#10;4. **配置打印机属性**  &#10;   打开“控制面板”，进入“硬件和设备”（或“设备和打印机”）。  &#10;   右键点击新安装的打印机，选择 **“打印机属性”**：  &#10;   - 修改打印机名称以便识别。  &#10;   - 设置 **“双面打印”** 功能。  &#10;   - 若打印机显示“脱机”，需在设置中取消 **SNMP** 状态检查。  &#10;   - 如需使用部门ID，请在“设备设置”-&gt;“管理员”中添加对应的部门ID（每机每部门ID不同）。&#10;&#10;**💡 提示**: &#10;- 安装过程中请确保网络连接正常，以便正确获取打印机IP。&#10;- 如遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于绑定邮箱，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **首次登录并绑定手机（新用户）**  &#10;   新用户初次使用263邮箱，必须在电脑网页端完成手机号绑定：&#10;   - 打开浏览器访问：https://www.263.net/&#10;   - 点击【登录】，输入邮箱账号和密码（若忘记密码可点击“忘记密码”重置）&#10;   - 输入手机号码和短信验证码，验证成功后即完成绑定&#10;&#10;2. **更换已绑定的手机号码**  &#10;   - **情况一：旧手机号仍可用**  &#10;     1. 登录邮箱，点击右上角【账户】头像 → 【设置】&#10;     2. 进入【账户信息】→ 点击【点击这里绑定手机】&#10;     3. 点击【解除绑定】，获取并输入验证码后确认解绑&#10;     4. 重新点击【绑定】，输入新手机号及验证码，完成绑定&#10;   - **情况二：旧手机号已注销或无法接收验证码**  &#10;     需通过OA系统发起流程变更：&#10;     1. 登录OA系统 → 点击【发起流程】→【IT类】→【IT服务】→【账户/权限申请】&#10;     2. “系统”选择&quot;263企业邮箱”，在“描述”中写明需求（如：原手机号已注销，需更换绑定新号码）&#10;&#10;3. **在企业微信中绑定263邮箱**  &#10;   - 打开企业微信 → 进入【工作台】→ 找到【263企业邮箱】应用&#10;   - 输入邮箱账号和密码即可完成绑定&#10;   - ⚠️ 注意：若刚重置过密码，需重新在企业微信中绑定才能正常使用&#10;&#10;**💡 提示**: &#10;- 邮箱账号务必与个人手机号绑定，以便找回密码和接收异地登录提醒&#10;- 不要将工作邮箱用于注册公共网站或发送私人邮件，确保公私分离&#10;- 如遇绑定失败、收不到验证码等问题，可通过OA提交IT报障单寻求帮助&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于登录零信任后无法进入BI系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认零信任客户端状态**  &#10;   确保您已成功安装并扫码登录了“安全助手(零信任)”客户端。登录后请勿退出，保持在线状态是访问内网应用（如BI平台）的前提。&#10;&#10;2. **检查浏览器与网址**  &#10;   在PC端使用浏览器打开BI平台官方网址：`https://bi.zy.com`。建议将该网址添加到收藏夹以便快速访问。&#10;&#10;3. **处理证书警告（如有）**  &#10;   如果浏览器提示“此服务器无法证明它是bi.p.it”或出现 `NET:ERR_CERT_AUTHORITY_INVALID` 错误：&#10;   - 点击页面上的【继续前往 bi.zy.com（不安全）】按钮；&#10;   - 即可进入集团通行证登录界面，通过验证码或企业微信扫码完成登录。&#10;&#10;4. **排查网络策略刷新问题**  &#10;   若已登录零信任但仍提示“无法访问此网页”：&#10;   - 关闭当前浏览器；&#10;   - 重新登录零信任客户端以刷新网络策略；&#10;   - 再次尝试访问BI平台。&#10;&#10;5. **检查DNS设置（针对Mac用户）**  &#10;   如果您使用的是Mac设备且遇到DNS相关报错（如“开启私网DNS失败”）：&#10;   - 进入系统网络设置，将本机网络的DNS地址中的 `127.0.0.1` 移除；&#10;   - 修改为自动获取DNS或联系IT帮助台获取最新安装包覆盖安装。&#10;&#10;6. **排除软件冲突**  &#10;   确认电脑上未运行旧版IOA软件（已停用），如有请卸载并重启电脑，避免与零信任产生冲突。&#10;&#10;**💡 提示**: &#10;- 零信任客户端需保持后台运行，退出后将导致内网应用无法访问；&#10;- 如遇持续无法访问，请联系IT帮助台获取最新版本安装包或进一步技术支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于零信任登录后界面为空的具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并解决IOA软件冲突**  &#10;   如果电脑上安装了旧版的IOA安全软件，可能会导致零信任客户端显示异常或应用列表空白。&#10;   - **解决方案**：请卸载IOA软件（该功能已不再使用），然后重启电脑。&#10;   - 重启后，重新扫码登录零信任客户端。&#10;&#10;2. **尝试刷新策略或重新登录**  &#10;   如果是临时网络策略未同步导致列表为空：&#10;   - 先关闭浏览器，点击零信任客户端的“刷新”按钮重新获取策略。&#10;   - 如果刷新无效，请退出零信任客户端，完全退出后再重新打开并扫码登录。&#10;&#10;3. **联系管理员处理组织架构问题**  &#10;   如果上述步骤无效，且您属于兼职老师或特定用户组，可能是账号未正确分配到对应的组织架构下（被分到了默认组）。&#10;   - **解决方案**：此情况需要零信任管理员人工介入，在后台将您的账号更改到正确的分组中。&#10;&#10;4. **检查控制器连接状态**  &#10;   确保零信任客户端已连接到正确的控制器地址。&#10;   - **操作**：在客户端设置中，确认控制器地址为 `124.71.208.207`。如果连接失败，可尝试切换控制器或重置控制器配置。&#10;&#10;**💡 提示**: &#10;- 登录零信任后，请勿随意退出客户端，否则可能导致应用访问权限失效。&#10;- 如果使用的是Mac系统且遇到DNS相关报错，请检查本机网络设置，移除指向 `127.0.0.1` 的DNS设置。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于清理C盘空间，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带磁盘清理工具**  &#10;   按下键盘上的 `Win` 键，在搜索框中输入“磁盘清理”，选择并打开该工具，按照提示选择C盘进行清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信客户端，依次点击：设置 &gt; 文件管理 &gt; 文件管理（查看当前存储路径）&gt; 更改。将存储路径修改为C盘以外的其他盘符（如D盘或E盘），保存后重启微信，即可释放大量C盘空间。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   打开企业微信客户端，进入：设置 &gt; 存储管理，根据提示将聊天记录和文件存储位置迁移至非C盘分区。&#10;&#10;4. **手动删除临时文件**  &#10;   按下 `Win + R` 键，输入 `%temp%` 并回车，打开临时文件夹。全选所有文件（Ctrl+A），然后删除（Shift+Delete可彻底删除）。注意：部分正在使用的文件可能无法删除，跳过即可。&#10;&#10;**💡 提示**: 在进行文件迁移或删除前，建议先备份重要数据；若操作中遇到问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上提交报障单获取支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于更换校区壁纸,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备壁纸文件**  &#10;   确保您的新壁纸图片格式为 **jpg**。如果是其他格式（如png），请先将其转换为jpg格式，并将文件名重命名为 **`1.jpg`**。  &#10;   *提示：若需查看文件扩展名，请在文件夹“查看”选项中勾选“文件扩展名”。*&#10;&#10;2. **备份当前壁纸**  &#10;   进入教学一体机 **D盘** 下的 **“壁纸”** 文件夹。  &#10;   将文件夹内现有的 `1.jpg` 文件重命名为 **`3.jpg`** 进行备份（以便未来需要恢复时使用）。&#10;&#10;3. **替换并生效**  &#10;   将您准备好的新壁纸文件（名为 `1.jpg`）复制粘贴到该“壁纸”文件夹中。  &#10;   返回教学一体机桌面，**等待约1分钟**，系统会自动更新显示新的桌面壁纸。&#10;&#10;**💡 提示**: &#10;- 请务必确保新图片命名为 `1.jpg` 且位于 D盘的“壁纸”文件夹内。&#10;- 如果操作中遇到问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何使用263邮箱发送大邮件，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认附件大小限制**  &#10;   263企业邮箱直接上传附件的大小限制为**30M**。如果您的邮件附件超过此大小，系统会提示“您发送的邮件大小超出了您的权限”。&#10;&#10;2. **使用Web端登录邮箱**  &#10;   请通过浏览器访问263企业邮箱网页版地址：`https://www.263.net` 进行登录。&#10;   *注意：客户端（如Outlook、Foxmail）通常不支持云附件功能，必须使用网页版。*&#10;&#10;3. **启用“云附件”功能**  &#10;   在撰写邮件时，不要直接添加本地大文件，而是点击工具栏中的**云附件**（或类似图标）功能。&#10;   - 将超过30M的文件上传至云端。&#10;   - 系统会自动生成一个下载链接插入到邮件正文中。&#10;&#10;4. **发送邮件**  &#10;   确认云附件链接已正确插入后，填写收件人并发送即可。&#10;   *提示：上传的云附件有效期为**15天**，请提醒收件人在有效期内下载。*&#10;&#10;**💡 提示**: &#10;- 如果是在手机APP上操作，部分版本可能也支持云附件功能，但最稳妥的方式是使用电脑网页版。&#10;- 云附件功能仅适用于单个或多个文件总大小超过30M的情况，小文件仍可直接作为普通附件发送。"/>
+        <filter val="好的!关于安装打印机,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备阶段：收集信息并下载驱动**&#10;   - **确认信息**：在开始安装前，请先获取打印机的**IP地址**和**型号**。如果是共用打印机，还需准备好部门密码。&#10;   - **下载驱动**：&#10;     - **Windows系统**：访问京瓷打印机驱动下载页面，将驱动包下载到电脑硬盘。&#10;     - **Mac系统**：访问京瓷打印机Mac系统驱动下载页面，下载对应的驱动包。&#10;&#10;2. **Windows系统安装步骤**&#10;   - **解压与启动**：解压下载的驱动包，进入文件夹双击运行 `Setup.exe`。&#10;   - **自定义安装**：接受协议后，选择“自定义安装”。&#10;   - **配置参数**：根据实际打印机的型号和IP地址填写相关信息，添加打印机驱动及升级组件。&#10;   - **完成安装**：按照提示完成安装流程。&#10;&#10;3. **Mac系统安装步骤**&#10;   - **运行安装程序**：双击下载的驱动包。若桌面未显示，可按 `Command + 空格键` 搜索 &quot;Kyocera OS X 10.9+ Web build 2024.05.16&quot; 并打开。&#10;   - **执行安装**：一路点击“继续”完成安装。&#10;   - **重启电脑**：安装完成后，**必须重启电脑**才能生效。&#10;   - **添加打印机**：&#10;     - 进入“系统偏好设置” &gt; “打印机与扫描仪”。&#10;     - 点击“添加”按钮，选择“IP连接”。&#10;     - 输入之前获取的打印机IP地址，选择对应的连接协议（如无法自动识别型号，请检查网线是否松动）。&#10;     - 完成添加后即可使用。&#10;&#10;4. **后续设置（可选）**&#10;   - **修改名称与双面打印**（Windows）：在控制面板的“设备和打印机”中，右键打印机选择“属性”，可修改名称或设置双面打印。&#10;   - **添加部门ID**：&#10;     - **Windows**：在打印机属性中进行设置。&#10;     - **Mac**：打开“应用程序”中的打印机程序，选择对应IP的打印机，添加部门ID。&#10;   - **解决脱机问题**：若打印机显示脱机，需在设置中取消SNMP状态。&#10;&#10;**💡 提示**: &#10;- 安装过程中请务必确保输入的IP地址和型号准确无误。&#10;- Mac用户安装驱动后务必重启电脑。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统 (http://oa.zy.com) 上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在MAC上安装打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并安装驱动包**  &#10;   首先访问京瓷打印机mac系统驱动下载页面获取驱动。安装前需确认打印机的IP地址（可通过打印机面板查看）。  &#10;   - 双击下载的驱动包进行安装。  &#10;   - 若桌面未找到文件，可按 `Command + 空格键` 打开搜索框，输入“Kyocera OS X 10.9+ Web build 2024.05.16”查找并双击运行。  &#10;   - 按照提示完成安装流程，**安装完成后务必重启电脑**。&#10;&#10;2. **添加打印机**  &#10;   重启后，进入“系统偏好设置” &gt; “打印机与扫描仪”。  &#10;   - 点击“+”号添加新打印机。  &#10;   - 选择“IP”标签页，输入之前记录的打印机IP地址，并选择合适的连接协议（如IPP、LPD等）。  &#10;   - 若无法自动识别型号，请检查打印机网络连接（如网线是否松动）。  &#10;   - 确认信息无误后完成添加，即可开始打印。&#10;&#10;3. **配置部门ID（如需）**  &#10;   若使用的是多功能一体机且需要部门ID：  &#10;   - 打开“应用程序”文件夹，找到并运行打印机管理程序。  &#10;   - 选择对应的IP打印机，按提示添加所属部门的ID。&#10;&#10;**💡 提示**: &#10;- 确保打印机已通电并连接到同一网络。&#10;- 若遇到连接问题，可尝试重新插拔网线或重启打印机。&#10;- 如有其他疑问，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决连接控制器地址sec.zy.com失败问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，在设置或连接选项中，将控制器地址手动修改为 `124.71.208.207`。&#10;&#10;2. **重置并重新输入控制器地址**  &#10;   如果切换地址后问题依旧，请选择“重置控制器”功能，然后再次手动输入新的控制器地址 `124.71.208.207` 进行连接。&#10;&#10;**💡 提示**: 此解决方案适用于 Windows 和 Mac 设备。如果执行上述步骤后仍无法连接，请检查本地网络环境是否正常，或联系IT帮助台获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于找回263邮箱密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置**  &#10;   打开【企业微信】，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，按照页面提示完成密码修改。&#10;&#10;2. **特殊情况处理（如手机已注销）**  &#10;   如果捆绑的旧手机号码已注销或无法接收验证码，需登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，在“系统”中选择&quot;263企业邮箱”，并在“描述”中说明变更手机号的需求。&#10;&#10;3. **更新客户端密码**  &#10;   密码重置成功后，如果您使用Outlook、Foxmail或Macbook邮件客户端，需要手动在这些软件中同步更新新密码，否则可能无法正常收发邮件。&#10;&#10;4. **重新绑定企业微信（如需）**  &#10;   若之前已通过企业微信绑定邮箱，重置密码后需重新进入【企业微信】-【工作台】-【263企业邮箱】，输入新密码完成重新绑定。&#10;&#10;**💡 提示**: &#10;- 新密码需包含大小写字母、数字和符号，长度不少于8位，且不能使用连续字符或简单密码。&#10;- 根据安全规定，首次登录及每90天需修改一次密码，特殊邮箱若90天内未修改将被停用。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重置263邮箱密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置（推荐）**  &#10;   打开【企业微信】，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，按页面提示完成密码修改。&#10;&#10;2. **通过网页端重置（需已绑定手机）**  &#10;   如果已绑定手机号码，可直接访问网址：`https://mm.263.com/wm2e/website/jsp/resetPassword.jsp` 进行密码重置。&#10;&#10;3. **更新客户端密码**  &#10;   密码重置成功后，如果您在 Outlook、Foxmail 或 Macbook 邮件等客户端中使用了该邮箱，需要手动更新登录密码才能正常收发邮件。&#10;&#10;4. **重新绑定企业微信（如适用）**  &#10;   若之前已通过企业微信绑定过263邮箱，密码重置后需重新进入【企业微信】-【工作台】-【263企业邮箱】，输入新密码完成重新绑定。&#10;&#10;**💡 提示**: &#10;- 新密码需包含大小写字母、数字和符号，长度不少于8位，且不能使用连续字符或简单密码。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于修改263企业邮箱密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置（推荐）**  &#10;   打开【企业微信】&gt; 点击【工作台】&gt; 选择【IT服务台】&gt; 进入【更多功能】&gt; 点击【邮箱密码重置】，按页面指引完成修改。&#10;&#10;2. **通过网页端直接修改（需已绑定手机）**  &#10;   访问网址：https://mm.263.com/wm2e/website/jsp/resetPassword.jsp，根据提示验证身份后修改密码。&#10;&#10;3. **同步更新客户端密码**  &#10;   如果您在电脑或手机上使用了邮件客户端（如 Outlook、Foxmail、Apple Mail），修改完网页密码后，请务必登录对应客户端，将旧密码更新为新密码，否则无法收发邮件。&#10;&#10;**💡 提示**: &#10;- **密码规则**：新密码长度需不小于8位，必须包含大写字母、小写字母、数字和符号，且不能使用连续字符或简单密码。&#10;- **安全提醒**：系统要求每90天修改一次密码，首次登录后也需立即修改。若特殊邮箱90天内未修改，账号将被停用。&#10;- **如遇问题**：可联系IT帮助台或在OA系统（http://oa.zy.com）填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于更改263邮箱密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置（推荐）**  &#10;   打开【企业微信】，点击【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】，按照页面提示完成新密码设置。&#10;&#10;2. **通过网页端直接修改（需已绑定手机）**  &#10;   如果你的手机号已绑定邮箱，可直接访问网址：`https://mm.263.com/wm2e/website/jsp/resetPassword.jsp` 进行密码修改。&#10;&#10;3. **更新客户端密码**  &#10;   如果你使用了 Outlook、Foxmail 或 Macbook Mail 等客户端，在修改完网页密码后，请务必同步更新客户端中的登录密码，否则会导致无法收发邮件。&#10;&#10;4. **特殊情况处理**  &#10;   - 如果旧手机号已注销无法接收验证码，需登录 OA 系统，发起流程：【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，选择“263企业邮箱”并描述需求以变更绑定手机。&#10;   - 如果登录时提示“用户邮箱状态异常”，请先按步骤1重置密码，然后重新在企业微信中绑定邮箱。&#10;&#10;**💡 提示**: &#10;- **密码规则**：新密码长度需不小于8位，必须包含大写字母、小写字母、数字和符号，且不能使用连续字符或简单密码。&#10;- **安全提醒**：根据安全管理要求，首次登录后及每90天需强制修改一次密码，否则账号可能被停用。&#10;- **同步修改**：修改密码后，所有绑定的邮件客户端（如Outlook、Mac Mail）都需要手动更新密码才能正常使用。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于Windows零信任卸载，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过控制面板卸载（常规方法）**  &#10;   按下键盘快捷键 `Win + R`，在运行框中输入 `control` 并回车打开控制面板。  &#10;   点击“卸载程序”（或“程序和功能”），在列表中找到“零信任”相关软件，双击进行卸载。&#10;&#10;2. **通过安全助手特权模式卸载（推荐方法）**  &#10;   *注意：如果系统中安装了“安全助手”，通常需要先卸载它才能顺利安装或重新配置零信任工具。*  &#10;   - **进入特权模式**：右键点击任务栏右下角的“安全助手”图标，选择“启动或显示托盘图标” -&gt; “更多” -&gt; “打开文件位置”。或者直接右键点击图标选择“特权模式”，输入管理员口令：**e2vPsv8$**。  &#10;   - **运行卸载程序**：进入特权模式后，找到本地路径 `C:\Windows\LVUAAgentInstBaseRoot`，运行其中的卸载文件。  &#10;   - **输入卸载码**：在弹出的窗口中输入安全助手卸载码：**e2vPsv8$**，确认后即可开始卸载。&#10;&#10;3. **直接定位安装目录卸载**  &#10;   - 按下 `Win` 键搜索“安全助手”，右键点击搜索结果中的“启动或显示托盘图标”，选择“更多” -&gt; “打开文件位置”。  &#10;   - 或者直接在文件资源管理器地址栏输入：`C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手` 并回车。  &#10;   - 在文件夹中找到卸载程序（通常为 Uninstall.exe 或类似名称），双击运行。  &#10;   - 输入管理员口令/卸载码：**e2vPsv8$**，按提示完成卸载。&#10;&#10;**💡 提示**: &#10;- 所有涉及密码的操作，管理员口令和卸载码均为：**e2vPsv8$**。&#10;- 如果卸载过程中遇到无法解决的问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;- 若需重新安装零信任工具，请确保先完成上述卸载步骤，再下载最新安装包进行覆盖安装。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何查看监控系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用Edge浏览器查看（推荐）**  &#10;   适用于临时或快速查看监控画面。&#10;   - 打开 **Microsoft Edge 浏览器**。&#10;   - 点击右上角三个点 `...` → 选择 **“设置”**。&#10;   - 在搜索框输入 `Explorer`，找到 **“允许在 Internet Explorer 模式下重新加载网站”**，选择 **“允许”**。&#10;   - 关闭并重启浏览器，右上角会出现 **“在 Internet Explorer 模式下重新加载”** 选项。&#10;   - 在地址栏输入监控 IP 地址：`192.168.0.X`（X 通常为 5~10）。&#10;   - 进入登录页面后，点击右上角三个点，选择 **“在 Internet Explorer 模式下重新加载”**。&#10;   - 输入账号密码登录：&#10;     - **有回放功能**：用户名 `userxq`，密码 `345110xq`&#10;     - **无回放功能**：用户名 `user`，密码 `345110jk`&#10;   - 首次使用会提示下载插件，按提示完成安装即可。&#10;   - 左上角点击 `e` 标志，开启兼容性模式，确保下次自动以 IE 模式打开。&#10;&#10;2. **使用 iVMS-4200 客户端查看（功能更全）**  &#10;   适用于需要回放、录像管理或自定义视图的场景。&#10;   - 打开 **iVMS-4200 3.13.0.5 客户端**。&#10;   - 点击右侧 **“设备管理”** → **“设备”** → **“添加”**。&#10;   - 输入设备信息：名称、IP 地址、用户名、密码（同上），点击 **“添加”**。&#10;   - 等待状态显示为 **“在线”** 表示连接成功。&#10;   - 如需切换账号（例如启用回放功能）：&#10;     - 在设备列表中选中对应设备，点击 **“笔形状图标”**。&#10;     - 修改为有回放权限的账号（如 `userxq` / `345110xq`）。&#10;   - 返回主界面，点击 **“主预览”** 查看实时画面。&#10;   - 可点击 **“自定义视图”** 创建分组（如“电梯间”、“通道”等），每组建议不超过 9 个画面以避免卡顿。&#10;&#10;**💡 提示**: &#10;- 若使用客户端时出现卡顿，建议采用“自定义预览分组”模式，按场景分类查看。&#10;- 所有摄像头需手动开启移动侦测、布防及视频丢失报警功能（每个通道单独设置）。&#10;- 如遇问题，可联系 IT 帮助台或在 OA 系统提交报障单（地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载零信任安装包,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认操作系统版本**  &#10;   请确认您的电脑是 Windows 还是 Mac (macOS) 系统，以便选择对应的安装包。&#10;&#10;2. **访问下载链接**  &#10;   - **Windows 用户**：点击以下链接下载最新版本安装包  &#10;     `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;   - **Mac 用户**：点击以下链接下载最新版本安装包  &#10;     `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg`&#10;&#10;3. **获取更新版本（可选）**  &#10;   如果您需要比上述链接更新的版本，可以通过企业微信联系 IT 帮助台获取。&#10;&#10;**💡 提示**: &#10;- 下载完成后，建议先检查文件完整性再运行安装。&#10;- 安装前请确保已卸载旧版“安全助手”（如有），或准备覆盖安装。&#10;- 安装过程中若需输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上安装打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **获取打印机信息并下载驱动**  &#10;   首先确认打印机的IP地址（可通过打印机面板查看）。然后访问京瓷官网下载适用于Mac系统的驱动程序。&#10;&#10;2. **安装驱动程序**  &#10;   - 双击下载的驱动包进行安装。  &#10;   - 若桌面未找到驱动文件，可按 `Command + 空格键` 打开搜索框，输入 `Kyocera OS X 10.9+ Web build 2024.05.16` 查找并双击运行。  &#10;   - 按照提示完成安装流程。  &#10;   - **重要**：安装完成后，请务必**重启电脑**。&#10;&#10;3. **添加打印机**  &#10;   - 进入“系统偏好设置” &gt; “打印机与扫描仪”。  &#10;   - 点击“+”号添加新打印机。  &#10;   - 选择“IP”标签页，输入之前获取的打印机IP地址，并选择合适的连接协议（如IPP、LPD等）。  &#10;   - 若无法自动识别型号，请检查打印机网络连接是否正常（如网线是否松动）。  &#10;   - 确认信息无误后完成添加，即可开始打印。&#10;&#10;4. **（可选）添加部门ID（针对一体打印机）**  &#10;   - 确保驱动已安装完毕。  &#10;   - 打开“应用程序”文件夹，找到并运行打印机管理程序。  &#10;   - 选择对应的IP打印机，按提示添加所属部门的ID。&#10;&#10;**💡 提示**: &#10;- 安装过程中如遇问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;- 部分共用打印机可能需要输入部门密码，请提前向管理员确认。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上连接和设置共享文件夹，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **连接共享服务器**&#10;   打开Finder，点击左上角菜单栏的【前往】(Go) - 【连接服务器】(Connect to Server)，或直接使用键盘快捷键 `Command + K`。&#10;   在弹出的窗口中输入校区共享盘地址：`smb://192.168.0.26`（注意：输入完需点击“+”号添加）。&#10;   点击【连接】后，系统会弹出登录窗口。&#10;&#10;2. **输入账号密码**&#10;   根据您所在的业务类型输入对应的用户名和密码：&#10;   *   **成长-班辅**：用户名为 `fdb`，密码为 `zy` + `校区名` + `fdb` (例如鸟巢校区密码为 `zyncfdb`)。&#10;   *   **亲子-个辅**：用户名为 `gf`，密码为 `zy` + `校区名` + `gf`。&#10;   *   **志业**：用户名为 `sgz`，密码为 `zy` + `校区名` + `sgz`。&#10;   *   **课室一体机**：用户名为 `ks`，密码为 `ks` (注：此账号仅拥有读取权限)。&#10;   输入完成后点击登录即可自动挂载共享盘。&#10;&#10;3. **设置开机自动挂载**&#10;   打开【系统偏好设置】，选择【用户与群组】。&#10;   在左侧列表中选择您的用户名，点击顶部的【登录项】标签。&#10;   将已挂载的网络驱动器图标从右侧列表拖放到下方的登录项列表中。&#10;   *可选*：勾选该条目下的【隐藏】框，这样系统启动时会自动挂载但不会自动打开Finder窗口。&#10;&#10;4. **创建桌面快捷方式**&#10;   在已连接的共享文件夹上点击【右键】，选择【创建快捷方式】。&#10;   此时桌面上会出现该文件夹的快捷访问路径，方便日常快速访问。&#10;&#10;**💡 提示**: &#10;*   如果您需要读写权限，请确保使用的是对应业务的账号（如 fdb, gf, sgz），ks账号仅限读取。&#10;*   如遇连接问题或密码错误，可联系IT帮助台或在OA系统 (http://oa.zy.com) 上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何登录零信任系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **安装客户端**  &#10;   确保电脑上已安装“安全助手（零信任）”客户端。若未安装，请运行安装包，同意协议后点击“安装”，等待完成。安装完成后桌面会出现“零信任”图标。&#10;&#10;2. **启动并扫码登录**  &#10;   双击桌面上的“零信任”图标打开软件。在登录界面选择“扫码登录”，使用企业微信扫描二维码即可完成认证。&#10;   *注意：如果首次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认后扫码。*&#10;&#10;3. **处理常见登录异常**  &#10;   - **提示“不合法的用户名”或“会话过期”**：返回上一级，选择“快捷方式登录”。&#10;   - **扫码认证失败**：重新进入扫码登录界面再次尝试。&#10;   - **无企业微信按钮**：重新打开软件，或点击控制切换器，手动输入 `124.71.208.207` 或 `sec.zy.com` 并确认。&#10;&#10;4. **验证登录状态**  &#10;   登录成功后，请勿退出零信任客户端。此时即可通过浏览器访问内部应用系统（如TMS、EVIP等）。&#10;&#10;**💡 提示**: &#10;- 登录前请确保电脑已卸载旧版IOA软件（如有），以免冲突导致无法访问内网。&#10;- 若遇到DNS相关错误（如“开启私网DNS失败”），请检查本机网络设置，移除DNS中的 `127.0.0.1` 设置，或联系IT帮助台获取最新安装包覆盖安装。&#10;- 登录过程中如遇第三方杀毒软件弹窗干扰，建议暂时禁用或卸载（如360、火绒等）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上安装打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **获取打印机信息并下载驱动**  &#10;   首先确认打印机的IP地址（可通过打印机面板查看）。然后访问京瓷官网下载适用于Mac系统的驱动程序。&#10;&#10;2. **安装驱动程序**  &#10;   - 双击下载的驱动包进行安装。  &#10;   - 若桌面未找到驱动文件，可按 `Command + 空格键` 打开搜索框，输入“Kyocera OS X 10.9+ Web build 2024.05.16”查找并双击运行。  &#10;   - 按照提示完成安装流程。  &#10;   - **重要**：安装完成后，请务必**重启电脑**。&#10;&#10;3. **添加打印机**  &#10;   - 进入“系统偏好设置” &gt; “打印机与扫描仪”。  &#10;   - 点击“+”号添加新打印机。  &#10;   - 选择“IP”标签页，输入之前获取的打印机IP地址，并选择合适的连接协议（如IPP、LPD等）。  &#10;   - 若无法自动识别型号，请检查打印机网络连接是否正常（如网线是否松动）。  &#10;   - 完成添加后，即可开始打印。&#10;&#10;4. **（可选）添加部门ID（针对一体机）**  &#10;   - 确保驱动已安装完毕。  &#10;   - 打开“应用程序”文件夹，找到并运行打印机程序。  &#10;   - 选择对应的IP打印机，按提示添加部门ID。&#10;&#10;**💡 提示**: &#10;- 安装前务必确认打印机IP地址和型号。&#10;- 若遇到网络识别问题，请检查物理连接或联系IT支持。&#10;- 如有其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于设置263企业邮箱初始密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置/设置密码**  &#10;   打开【企业微信】&gt; 点击【工作台】&gt; 选择【IT服务台】&gt; 点击【更多功能】&gt; 选择【邮箱密码重置】。按照页面指引输入新密码并完成设置。&#10;   *注：此方法适用于首次设置或忘记密码的情况。*&#10;&#10;2. **通过网页端修改（如已绑定手机）**  &#10;   如果已绑定手机号，可直接访问网址 `https://mm.263.com/wm2e/website/jsp/resetPassword.jsp` 进行密码修改。&#10;&#10;3. **确认密码符合安全规则**  &#10;   在设置新密码时，请确保满足以下要求：&#10;   - 长度不小于8位&#10;   - 包含大写字母、小写字母、数字和符号&#10;   - 不能使用连续字符（如123456）或简单密码&#10;&#10;**💡 提示**: &#10;- 根据安全管理要求，首次登录及每90天需修改一次密码，否则账号可能被停用。&#10;- 若使用Foxmail、Outlook等客户端，修改密码后需同步更新客户端中的密码。&#10;- 如遇“用户邮箱状态异常”提示，请先完成上述密码重置流程，再重新绑定企业微信。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决邮箱密码被锁问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置密码**  &#10;   打开【企业微信】，点击【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】。按照页面提示的步骤完成新密码的修改。&#10;&#10;2. **通过网页端重置密码（需已绑定手机）**  &#10;   如果您的邮箱账号已绑定手机号码，可以直接访问网址：`https://mm.263.com/wm2e/website/jsp/resetPassword.jsp`，根据指引进行密码重置。&#10;&#10;3. **同步更新客户端密码**  &#10;   密码修改成功后，如果您使用 Foxmail、Outlook 或 Macbook 邮件客户端，请务必在客户端中同步更新新的登录密码，否则会导致无法收发邮件。&#10;&#10;4. **联系IT帮助台（如上述方法无效）**  &#10;   如果自助重置失败或遇到其他特殊情况，可联系IT帮助台，或在OA系统（地址：http://oa.zy.com）上填写IT报障单寻求人工协助。&#10;&#10;**💡 提示**: &#10;- 密码规则要求：必须包含大小写字母、数字和符号，长度不小于8位，且不能使用连续字符或简单密码。&#10;- 根据安全规定，邮箱密码每90天需强制修改一次，首次登录后也需立即修改。&#10;- 建议将邮箱账号与个人手机号绑定，以便接收异地登录提醒并辅助找回密码。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于连接公司打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备信息**  &#10;   在开始安装前，请先确认以下信息：&#10;   - **打印机IP地址**：查看打印机屏幕或打印网络配置页获取。&#10;   - **打印机型号**：查看打印机机身正面标识。&#10;   - **部门密码/ID**（如适用）：部分共用打印机需输入特定部门ID。&#10;&#10;2. **根据系统选择安装方式**&#10;&#10;   **🍎 Mac 系统用户：**&#10;   - **下载驱动**：访问京瓷官网下载对应Mac系统的驱动包（文件名通常包含 `Kyocera OS X`）。&#10;   - **安装驱动**：双击驱动包进行安装，若桌面未找到，可使用 `Command + 空格` 搜索“Kyocera”并打开。**安装完成后必须重启电脑**。&#10;   - **添加打印机**：&#10;     1. 进入“系统偏好设置” &gt; “打印机与扫描仪”。&#10;     2. 点击“+”号添加，选择“IP”标签页。&#10;     3. 输入打印机IP地址，协议选择默认或自动检测。&#10;     4. 完成添加后即可打印。&#10;   - **设置部门ID**（如需）：打开“应用程序”中的打印机程序，选择对应IP的打印机，输入部门ID。&#10;&#10;   **💻 Windows 系统用户：**&#10;   - **下载驱动**：访问京瓷官网下载驱动包并保存到硬盘。&#10;   - **安装驱动**：&#10;     1. 解压驱动包，双击 `Setup.exe`。&#10;     2. 接受协议，选择“自定义安装”。&#10;     3. 按提示输入打印机型号和IP地址，完成组件安装。&#10;   - **添加打印机**：&#10;     1. 打开“控制面板” &gt; “设备和打印机”。&#10;     2. 右键点击已安装的打印机，选择“打印机属性”。&#10;     3. 修改名称（可选），并在“端口”选项卡中确认IP地址正确。&#10;   - **设置部门ID**（如需）：&#10;     1. 在“打印机属性”中点击“设备设置” &gt; “管理员”。&#10;     2. 输入对应的部门ID（每机每部门ID不同）。&#10;   - **故障排查**：若显示“脱机”，请在属性中取消勾选“SNMP状态启用”。&#10;&#10;**💡 提示**: &#10;- 确保打印机网线连接正常，网络通畅。&#10;- 如遇问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上连接打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并安装驱动**&#10;   - 访问京瓷打印机mac系统驱动下载页面获取驱动包。&#10;   - **注意**：安装前需先确认打印机的IP地址（通常贴在打印机标签纸上）。&#10;   - 双击驱动包进行安装；若桌面未找到文件，可按 `Command + 空格键` 打开搜索框，输入“Kyocera OS X 10.9+ Web build 2024.05.16”查找并双击安装。&#10;   - 按照提示完成安装流程，**安装完成后务必重启电脑**。&#10;&#10;2. **添加打印机**&#10;   - 进入“系统偏好设置”，点击“打印机与扫描仪”。&#10;   - 点击“+”号添加新打印机。&#10;   - 选择“IP”标签页，输入之前获取的打印机IP地址，并选择合适的连接协议。&#10;   - 若电脑无法自动识别型号，请检查打印机网络连接（如网线是否松动）。&#10;   - 完成添加后，即可进行打印测试。&#10;&#10;3. **（可选）添加部门ID**&#10;   - 若使用的是多功能一体机且需要部门ID，请先确保驱动已安装。&#10;   - 打开“应用程序”文件夹，找到并双击打印机程序。&#10;   - 选择对应的IP打印机，按提示添加部门ID。&#10;&#10;**💡 提示**: &#10;- 安装驱动后必须重启电脑才能生效。&#10;- 如果添加过程中遇到网络问题或无法识别设备，请检查物理连接。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在MAC上安装零信任，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载MAC版安装包**  &#10;   访问以下链接下载MAC版本的零信任客户端：  &#10;   https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg  &#10;   *注：如需获取最新版本，可通过企业微信联系IT帮助台。*&#10;&#10;2. **运行并安装软件**  &#10;   - 双击下载的 `.dmg` 文件进行挂载。&#10;   - 将“零信任”应用图标拖拽到“应用程序”文件夹中完成安装。&#10;   - 安装完成后，打开“应用程序”找到“零信任”并启动。&#10;&#10;3. **扫码登录**  &#10;   - 启动零信任后，使用手机扫描屏幕上的二维码进行登录。&#10;   - 如果首次安装提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认后继续扫码登录。&#10;&#10;4. **验证连接**  &#10;   - 登录成功后，即可通过浏览器访问内部系统（如TMS、EVIP等）。&#10;   - 若遇到无法访问网页的情况，请关闭浏览器，重新登录零信任并刷新策略。&#10;&#10;**💡 提示**: &#10;- 安装前请确保未运行其他可能冲突的安全软件（如IOA、第三方杀毒软件等）。&#10;- 若安装后出现DNS异常（如本地DNS被设置为127.0.0.1），请在“系统设置 &gt; 网络”中将其删除或改为自动获取。&#10;- 如遇“开启私网DNS失败”等错误，建议联系IT帮助台获取最新安装包覆盖安装。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于预数系统的账号密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **获取登录凭证**  &#10;   系统使用**员工通行证**作为登录账号和密码。请直接使用您公司的员工通行证账号及对应密码进行登录。&#10;&#10;2. **处理忘记密码的情况**  &#10;   如果您修改过密码但忘记了，可以通过以下地址找回：  &#10;   https://ucin.zy.com/forgot_password&#10;&#10;3. **访问系统入口**  &#10;   在浏览器（推荐使用谷歌浏览器）中输入系统地址：  &#10;   https://jyys.zy.com/jyys/admin/login  &#10;   输入上述账号密码即可进入系统。&#10;&#10;**💡 提示**: &#10;- 请确保使用**谷歌浏览器**访问，以获得最佳兼容性。&#10;- 如果无法登录，请先确认您的员工通行证状态是否正常，或联系IT部门重置密码。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决零信任用户名不合法问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **返回上一级界面**  &#10;   在登录页面提示“不合法的用户名”时，不要直接输入用户名，先点击界面上的“返回”或“上一级”按钮。&#10;&#10;2. **选择快捷方式登录**  &#10;   在返回后的主界面中，找到并点击“快捷方式登录”选项（通常用于扫码登录），跳过手动输入用户名的步骤。&#10;&#10;3. **重新进行扫码认证**  &#10;   使用企业微信或其他指定工具扫描屏幕上的二维码完成登录。如果之前是扫码失败导致该提示，请确保网络正常后再次尝试。&#10;&#10;**💡 提示**: &#10;- 此问题通常是因为系统检测到手动输入的用户名格式错误或会话过期，切换为“快捷方式登录”可自动获取正确的认证信息。&#10;- 如果多次尝试仍无效，建议退出零信任客户端，完全关闭后重新打开再试。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于苹果电脑首次登录企业微信无法连接控制器问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并切换控制器地址**  &#10;   打开零信任客户端，在设置或连接界面中，手动将控制器地址修改为：**124.71.208.207**。这是解决“连接控制器失败”提示的首选方案。&#10;&#10;2. **重置控制器配置（如步骤1无效）**  &#10;   如果切换地址后仍无法连接，请在客户端中选择“重置控制器”功能，然后重新输入控制器地址 **124.71.208.207** 进行保存和重连。&#10;&#10;3. **修复系统 hosts 文件（针对 JavaScript 错误导致无法启动）**  &#10;   如果启动时提示&quot;JavaScript 错误”导致无法正常启动：&#10;   - 打开 Mac 的“终端”应用；&#10;   - 输入命令 `sudo vi /etc/hosts` 并按回车（需输入开机密码）；&#10;   - 在文件中添加一行：`127.0.0.1 localhost`；&#10;   - 保存退出后重启零信任客户端。&#10;&#10;4. **确认浏览器兼容性（如访问应用报 403）**  &#10;   若 nslookup 解析正常但 Safari 或 Firefox 访问应用报错 403，请尝试更换为 **Google Chrome 浏览器** 进行访问。&#10;&#10;5. **使用企业微信扫码登录**  &#10;   确保已安装最新版本的零信任客户端（Mac 版下载地址见指引），安装完成后直接通过**企业微信扫码**进行登录认证，避免手动输入账号密码可能带来的兼容性问题。&#10;&#10;**💡 提示**: &#10;- 请确保您的 Mac 系统已更新到较新版本，且网络连接正常。&#10;- 若上述步骤均无效，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）提交报障单获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于绑定263企业邮箱手机号，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **新用户首次登录绑定**  &#10;   如果您是初次使用263邮箱，必须在电脑网页端完成绑定：&#10;   - 打开浏览器访问网址：`https://www.263.net/`&#10;   - 点击【登录】，输入您的邮箱账号和密码。&#10;   - 在验证环节，输入您的【手机号码】和收到的【短信验证码】。&#10;   - 提示“手机号验证成功”即表示绑定完成。&#10;&#10;2. **更换或重新绑定手机号（旧号可用）**  &#10;   如果您需要更换绑定的手机号，且旧手机号仍能接收短信：&#10;   - 登录网页版邮箱，点击右上角【账户】头像，选择【设置】。&#10;   - 进入【账户信息】，点击【点击这里绑定手机】。&#10;   - 先点击【解除绑定】，获取并输入旧手机号的验证码以解绑。&#10;   - 解绑成功后，点击【绑定】，输入新的【手机号码】和验证码，点击确定即可完成新号码绑定。&#10;&#10;3. **更换或重新绑定手机号（旧号已注销/无法接收短信）**  &#10;   如果旧手机号已注销或无法接收验证码，需通过OA系统申请变更：&#10;   - 登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】。&#10;   - 在“系统”选项中选择&quot;263企业邮箱”。&#10;   - 在“描述”栏中清楚写明您的需求（例如：原手机号已注销，申请变更绑定新手机号）。&#10;   - 提交流程等待IT部门处理。&#10;&#10;4. **手机端App绑定异常处理**  &#10;   如果在手机App登录时提示“绑定的手机号码已经变更”：&#10;   - 请先使用电脑浏览器登录 `mail.zy.com` (或 `www.263.net`)。&#10;   - 按照上述第2步的方法，在网页端将手机号更改为当前可用的号码并保存。&#10;   - 更改完成后，再回到手机App重新登录即可。&#10;&#10;**💡 提示**: &#10;- 密码重置后，如果需要继续使用企业微信绑定邮箱，请记得重新在企业微信中绑定一次。&#10;- 确保输入的手机号准确无误，且能正常接收短信验证码。&#10;- 如遇其他问题，可联系IT帮助台或在OA上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何切换监控软件用户，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开设备管理界面**  &#10;   启动监控客户端“iVMS-4200”，在主菜单界面的右侧找到并点击【设备管理】。&#10;&#10;2. **选择目标监控设备**  &#10;   在设备列表中，选中您需要修改账号的监控设备。&#10;&#10;3. **进入编辑模式**  &#10;   点击该设备旁边的**笔形状图标**（编辑按钮），进入账号设置页面。&#10;&#10;4. **修改登录凭证**  &#10;   将当前的用户名和密码修改为具有回放功能的账号信息：&#10;   - **有回放功能账号**：用户名 `userxq`，密码 `345110xq`&#10;   - *(注：普通无回放账号为 user / 345110jk，若需查看录像请务必使用前者)*&#10;&#10;5. **确认连接状态**  &#10;   保存设置后，观察设备状态显示为&quot;**在线**&quot;，即表示切换成功且连接正常。&#10;&#10;**💡 提示**: &#10;- 切换账号的主要目的是为了获取**视频回放权限**。&#10;- 如果操作中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何登录BI系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **前置准备：确保已登录企业微信（0信任）**  &#10;   在访问BI平台之前，请确保您的企业微信（文中称为&quot;0信任&quot;）已经处于正常登录状态。这是后续单点登录或扫码登录的基础。&#10;&#10;2. **打开BI平台网址**  &#10;   在电脑端浏览器中打开以下网址：  &#10;   `https://bi.zy.com`  &#10;   *建议将该网址添加到浏览器收藏夹，以便日后快速访问。*&#10;&#10;3. **处理安全证书提示（如出现）**  &#10;   如果是首次访问，浏览器可能会弹出“您的连接不是私密连接”或“NET:ERR_CERT_AUTHORITY_INVALID”等安全警告。  &#10;   - 请点击页面上的 **【高级】** 按钮。  &#10;   - 选择 **【继续前往 bi.zy.com（不安全）】** 即可进入登录界面。&#10;&#10;4. **执行登录操作**  &#10;   进入集团通行证登录界面后，您有两种登录方式：  &#10;   - **验证码登录**：输入账号并获取验证码进行验证。  &#10;   - **企业微信扫码登录**：直接使用已登录的企业微信扫描二维码完成登录。&#10;&#10;5. **确认权限与角色**  &#10;   登录成功后，您将看到BI平台主界面。  &#10;   - **只读用户**：如果您是通过卓越通行证加入的用户，默认为“只读用户”，主要查看仪表板数据。  &#10;   - **普通用户/管理员**：如需新增、编辑数据源或制作看板，需提前通过OA流程申请相应权限（提单人-直接上级-ITBP审批）。&#10;&#10;**💡 提示**: &#10;- 如果登录后看不到预期的仪表板，可能是权限未开通或属于不同的用户组，请联系系统管理员（曹思琴）或通过OA流程申请权限。&#10;- 遇到证书报错是正常现象，按上述步骤点击“继续前往”即可正常使用，不影响数据安全。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上连接打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并安装驱动**&#10;   - 访问京瓷打印机mac系统驱动下载页面获取驱动包。&#10;   - **注意**：安装前需先确认打印机的IP地址（通常贴在打印机标签纸上）。&#10;   - 双击驱动包进行安装；若桌面未找到文件，可按 `Command + 空格键` 打开搜索框，输入“Kyocera OS X 10.9+ Web build 2024.05.16”查找并双击安装。&#10;   - 按照提示完成安装流程，**安装完成后务必重启电脑**。&#10;&#10;2. **添加打印机**&#10;   - 进入“系统偏好设置”，点击“打印机与扫描仪”。&#10;   - 点击“+”号添加新打印机。&#10;   - 选择“IP”标签页，输入之前获取的打印机IP地址，并选择合适的连接协议。&#10;   - 若电脑无法自动识别型号，请检查打印机网络连接（如网线是否松动）。&#10;   - 完成添加后，即可进行打印测试。&#10;&#10;3. **配置部门ID（针对一体打印机）**&#10;   - 确保驱动已安装完毕。&#10;   - 打开“应用程序”文件夹，找到并双击打开打印机程序。&#10;   - 选择对应的IP打印机，点击“添加部门ID”并按提示输入相应信息。&#10;&#10;**💡 提示**: &#10;- 每台打印机和每个部门的ID可能不同，请根据实际要求填写。&#10;- 如遇非驱动或网络问题（如卡纸、硒鼓故障等），可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重置内部通行证密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开企业微信**  &#10;   登录您的企业微信账号。&#10;&#10;2. **进入IT服务台**  &#10;   点击底部菜单栏的【工作台】，在应用列表中找到并点击【IT服务台】。&#10;&#10;3. **选择更多功能**  &#10;   在IT服务台页面中，点击右下角或底部的【更多功能】选项。&#10;&#10;4. **执行密码重置**  &#10;   在功能列表中找到并点击【通行证密码重置】，按照页面提示完成后续验证及新密码设置。&#10;&#10;**💡 提示**: &#10;- 通行证使用时**不带** `@zy.com` 的后缀。&#10;- 请注意区分：通行证密码**不是**邮箱密码（邮箱密码需通过“邮箱密码重置”功能单独处理）。&#10;- 如操作中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于苹果电脑零信任转圈圈问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查“完全磁盘访问权限” (适用于 Intel 芯片 Mac)**  &#10;   如果您的设备是 Mac (Intel x86) 且遇到“零信任登录”一直转圈圈：  &#10;   - 打开 **系统设置** &gt; **隐私与安全性** &gt; **完全磁盘访问权限**。  &#10;   - 在列表中找到并允许以下两个进程：  &#10;     - `dvc-filemonitor-exe`  &#10;     - `dvc-screen-exe`  &#10;   - 如果上述方法无效，可能属于深层权限问题，需联系中后台安全对接群解决。&#10;&#10;2. **检查“系统扩展程序”权限 (适用于 Apple Silicon/ARM 芯片 Mac)**  &#10;   如果您的设备是 Mac (ARM) 且安装或运行时“系统扩展程序”功能一直转圈圈：  &#10;   - 打开 **设置** &gt; **安全性与隐私**。  &#10;   - 找到提示“来自应用程序 'Kaspersky Endpoint Security Daemon' 的系统软件已被阻止载入”。  &#10;   - 点击 **允许** 以授权该程序运行。&#10;&#10;3. **处理提权密码错误导致的卡死**  &#10;   如果是因为输入密码提权时提示不对导致界面卡住：  &#10;   - 进入 **设置** &gt; **隐私与安全性**，确保已添加零信任程序并开启 SDP 相关权限。  &#10;   - 检查输入的密码是否包含特殊字符串，如有请修改后重新尝试提权。&#10;&#10;4. **重置控制器地址 (通用方案)**  &#10;   如果上述权限设置无误但仍无法连接：  &#10;   - 在零信任客户端中选择切换控制器地址为 `124.71.208.207`。  &#10;   - 若仍不解决，尝试重置控制器配置后再次输入该地址。&#10;&#10;**💡 提示**: &#10;- 不同芯片架构（Intel vs ARM）的解决方案不同，请先确认您的 Mac 型号。&#10;- 如果涉及第三方杀毒软件冲突，建议暂时卸载如 360、火绒等软件后再试。&#10;- 若所有步骤均无效，可能是账号组分配或网络策略问题，请联系零信任管理员协助排查。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**如何卸载零信任**,具体操作如下:&#10;&#10;由于您未说明操作系统，以下分别提供 **Windows** 和 **Mac** 系统的卸载步骤，请根据您的电脑类型选择对应方案。&#10;&#10;### 🪟 Windows 系统卸载步骤&#10;&#10;**方法一：通过控制面板卸载（推荐）**&#10;1. **打开控制面板**  &#10;   按下键盘快捷键 `Win + R`，在运行框中输入 `control` 并回车。&#10;2. **进入程序卸载界面**  &#10;   点击“卸载程序”（或“程序和功能”）。&#10;3. **执行卸载**  &#10;   在列表中找到“零信任”相关软件，双击它并按照提示完成卸载。&#10;&#10;**方法二：通过安全助手特权模式卸载（若方法一无效）**&#10;*注：此方法适用于需要输入管理员口令的情况。*&#10;1. **进入特权模式**  &#10;   右键点击桌面上的“安全助手”图标，选择“启动或显示托盘图标”，点击“更多” -&gt; “打开文件位置”。&#10;2. **运行卸载程序**  &#10;   在文件夹中找到卸载程序（通常位于 `C:\Windows\LVUAAgentInstBaseRoot` 目录下），双击运行。&#10;3. **输入密码**  &#10;   当提示输入管理员口令或卸载码时，输入：**`e2vPsv8$`**。&#10;4. **完成卸载**  &#10;   确认后即可开始卸载流程。&#10;&#10;---&#10;&#10;### 🍎 Mac 系统卸载步骤&#10;&#10;1. **退出零信任应用**  &#10;   确保零信任客户端已完全关闭（否则无法卸载）。&#10;2. **移至废纸篓**  &#10;   点击屏幕顶部菜单栏的“前往” -&gt; “应用程序”，找到“零信任”图标，右键点击并选择“移到废纸篓”。&#10;3. **清理 DNS 设置**  &#10;   - 打开“系统设置” -&gt; “网络”。&#10;   - 检查 DNS 设置中是否有 `127.0.0.1`，如果有，请将其删除并保存；如果没有则跳过此步。&#10;4. **终端清理残留（可选）**  &#10;   - 打开“实用工具”中的“终端”。&#10;   - 根据提示输入命令进行深度清理（需输入开机密码，输入时密码不会显示，直接输入后回车即可）。&#10;&#10;---&#10;&#10;**💡 提示**: &#10;- **Windows 卸载密码**：如果卸载过程中要求输入密码，统一使用 **`e2vPsv8$`**。&#10;- **安装顺序**：如果您计划重新安装，请先彻底卸载旧版本（如安全助手），再安装新的零信任工具。&#10;- **遇到问题**：如操作中遇到其他问题，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上实现微信双开，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **清理旧文件（如之前安装过）**  &#10;   如果您之前尝试过微信多开，建议先彻底清除旧文件。打开【终端】程序，输入以下命令并回车（将 `XX` 替换为您之前的多开应用名称，例如 `WeChat2.app`）：&#10;   ```bash&#10;   sudo rm -rf /Applications/XX.app&#10;   ```&#10;   *注：执行此命令可能需要输入管理员密码。*&#10;&#10;2. **创建自动操作脚本**  &#10;   1. 点击屏幕底部的【启动台】图标。&#10;   2. 在顶部搜索框中输入【自动】，然后按回车键，点击出现的【自动操作】应用程序。&#10;   3. 在菜单栏选择【文件】&gt;【新建文稿】，在弹出的窗口中选择【运行Shell脚本】。&#10;&#10;3. **输入双开命令**  &#10;   在脚本编辑区域中，删除默认内容，粘贴以下命令：&#10;   ```bash&#10;   nohup /Applications/WeChat.app/Contents/MacOS/WeChat &gt; /dev/null 2&gt;&amp;1 &amp;&#10;   ```&#10;   *说明：如果您需要开启更多个微信（例如4开），请复制该命令多次，每行一条。*&#10;&#10;4. **保存并命名**  &#10;   1. 点击【文件】&gt;【存储】。&#10;   2. 在弹窗中设置参数，将“存储为”设置为您想要的名字（例如“微信双开”）。&#10;   3. 确保格式选择为【应用程序】。&#10;&#10;5. **启动双开微信**  &#10;   保存完成后，回到【启动台】，您会看到刚刚创建的自定义程序图标。点击该图标，即可启动第二个微信实例，实现双开效果。&#10;&#10;**💡 提示**: &#10;- 如果在使用过程中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;- 此方法适用于macOS系统，请确保您的微信版本支持多开功能。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何输入零信任控制器地址，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **启动或安装零信任客户端**  &#10;   打开“安全助手（零信任）”客户端。如果是首次安装，在运行安装程序并点击“安装”后，系统可能会自动弹出设置界面；如果已安装但需重新配置，请尝试退出并重新启动客户端。&#10;&#10;2. **进入控制器地址设置界面**  &#10;   - 若客户端启动时直接提示需要输入控制器地址，请在弹窗中输入以下任一地址：  &#10;     `sec.zy.com` 或 `124.71.208.207`  &#10;   - 若客户端已连接但出现“连接控制器失败”等错误，可在客户端界面中找到“切换控制器”或类似选项，手动将地址修改为 `124.71.208.207`。&#10;&#10;3. **确认并保存设置**  &#10;   输入地址后，点击“确认”或“确定”按钮。系统将尝试连接该控制器。连接成功后，即可进行扫码登录等操作。&#10;&#10;4. **如遇连接失败，尝试重置控制器**  &#10;   如果切换地址后仍无法连接，可选择“重置控制器”功能（通常在设置或帮助菜单中），然后再次手动输入 `124.71.208.207` 并确认。&#10;&#10;**💡 提示**:  &#10;- 推荐使用的标准控制器地址为：**124.71.208.207**。  &#10;- 确保电脑网络连接正常，且未开启可能干扰网络设置的第三方杀毒软件或代理工具。  &#10;- Mac用户若遇到JavaScript错误或DNS问题，可参考相关FAQ检查 `/etc/hosts` 文件或清除本地DNS设置。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何安装监控软件，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载客户端**  &#10;   复制以下链接到浏览器打开并下载 iVMS-4200 客户端安装包：  &#10;   https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;2. **以管理员身份运行安装**  &#10;   找到下载好的 `ivms-4200` 海康软件安装包，**右击**选择【以管理员身份运行】，在弹出的提示框中选择【是】。&#10;&#10;3. **接受协议并配置安装选项**  &#10;   - 勾选【我接受许可证协议条款】，单击【下一步】。&#10;   - 在“请选择要安装的功能”界面，**只勾选【视频】**功能。&#10;   - 在“目标文件夹”处，建议切换到**非C盘**进行安装（例如D盘），然后单击【安装】按钮。&#10;&#10;4. **设置账号与密码**  &#10;   安装完成后，首次使用需设置监控用户名和密码：&#10;   - **默认用户名**：`user`&#10;   - **默认密码**：`345110jk`&#10;   - **密保问题**：统一档案是 `1`&#10;&#10;5. **添加设备**  &#10;   打开软件进入主界面，点击左侧菜单的【设备管理】—【设备】，按照提示添加录像机设备。&#10;&#10;**💡 提示**: &#10;- 若后续需要查看回放功能，请确保设备账号切换为有回放权限的账号（用户名：`userxq`，密码：`345110xq`）。&#10;- 如安装或使用过程中遇到问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于查看打印机IP地址,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **查看机身标签**  &#10;   大多数打印机的IP地址会直接粘贴或写在机身的标签纸上。请仔细检查打印机机身（通常在侧面、背面或出纸口附近），找到印有网络信息或IP地址的标签即可。&#10;&#10;2. **联系IT支持（如无法查看）**  &#10;   如果标签丢失或无法看清，您可以：&#10;   - 联系IT帮助台；&#10;   - 或在OA系统（http://oa.zy.com）上填写IT报障单进行查询。&#10;&#10;**💡 提示**: &#10;- 在Windows系统中修改或安装打印机时，通常也需要先获取该IP地址。&#10;- 若遇到打印机无法开机、卡纸等硬件问题，可拨打报修电话或添加“穗保客服”微信进行咨询。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重设预数系统密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问密码找回页面**  &#10;   打开浏览器，在地址栏输入以下链接：  &#10;   `https://ucin.zy.com/forgot_password`&#10;&#10;2. **使用员工通行证找回**  &#10;   在页面中输入您的**员工通行证账号**，按照页面提示完成验证并设置新密码。&#10;&#10;3. **登录系统**  &#10;   密码重置成功后，返回预数系统登录页（`https://jyys.zy.com/jyys/admin/login`），使用新的密码进行登录。&#10;&#10;**💡 提示**: &#10;- 请确保使用**谷歌浏览器**进行操作，以获得最佳兼容性。&#10;- 如果您从未修改过密码，默认通常使用初始分配的员工通行证密码；若已修改但忘记，请务必通过上述找回链接处理。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决零信任无法连接控制器问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，找到控制器设置选项，将控制器地址手动修改为：**124.71.208.207**。这是推荐的官方控制器地址。&#10;&#10;2. **重置并重新输入控制器地址**  &#10;   如果切换地址后问题依旧：&#10;   - 选择“重置控制器”功能；&#10;   - 重新输入控制器地址：**124.71.208.207**；&#10;   - 保存设置并重启零信任客户端。&#10;&#10;3. **检查网络与DNS设置（针对Mac用户）**  &#10;   如果是Mac设备且仍无法连接：&#10;   - 打开终端，执行命令：`sudo vi /etc/hosts`；&#10;   - 确保文件中包含一行：`127.0.0.1 localhost`；&#10;   - 保存退出后重启客户端。&#10;&#10;4. **确认无软件冲突**  &#10;   检查是否安装了已停用的IOA软件或其他第三方安全软件（如360、火绒等），如有请卸载并重启电脑，避免干扰零信任运行。&#10;&#10;**💡 提示**: &#10;- 确保网络连接正常，防火墙未阻止零信任客户端通信；&#10;- 若使用企业微信扫码登录失败，可尝试返回上一级选择“快捷方式登录”；&#10;- 如问题仍未解决，建议联系IT帮助台获取最新安装包或进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于安装悦智学打印插件，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开火狐浏览器并进入配置页面**  &#10;   启动火狐浏览器（Firefox），在地址栏输入 `about:config` 并按回车键。&#10;&#10;2. **搜索安全协议设置**  &#10;   在弹出的搜索框中输入 `security.tls.version.min`。&#10;&#10;3. **处理安全警告**  &#10;   系统可能会弹出“面临潜在的安全风险”的警告提示（提示检测到 localhost 访问威胁）。&#10;   *   请点击页面上的 **“详细了解”** 或类似确认按钮。&#10;   *   选择继续访问以忽略该安全警告。&#10;&#10;4. **执行插件安装**  &#10;   在成功绕过安全限制后，点击页面上的 **“TMS点击执行安装”** 按钮，即可完成打印机插件的安装。&#10;&#10;**💡 提示**: &#10;*   此操作涉及修改浏览器的底层安全配置，请确保您是在受信任的内部网络环境下进行。&#10;*   如果安装过程中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**卸载安全助手**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **获取管理员口令与卸载码**  &#10;   在开始操作前，请准备好以下关键信息（两者相同）：  &#10;   - **管理员口令**：`e2vPsv8$`  &#10;   - **安全助手卸载码**：`e2vPsv8$`  &#10;&#10;2. **方式一：通过特权模式卸载（推荐）**  &#10;   - 右键点击桌面或任务栏的**安全助手图标**。  &#10;   - 选择进入**特权模式**，输入管理员口令 `e2vPsv8$` 确认进入。  &#10;   - 打开文件资源管理器，定位到路径：`C:\Windows\LVUAAgentInstBaseRoot`。  &#10;   - 找到并运行该目录下的卸载程序。  &#10;   - 当提示输入密码时，输入卸载码 `e2vPsv8$` 完成卸载。&#10;&#10;3. **方式二：通过安装目录直接卸载**  &#10;   - 按下键盘上的 **Win键**，搜索“安全助手”。  &#10;   - 右键点击搜索结果中的“启动或显示托盘图标”，选择**更多** &gt; **打开文件位置**。  &#10;   - 或者直接在地址栏输入路径：`C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手` 并回车。  &#10;   - 在打开的文件夹中，双击运行卸载程序。  &#10;   - 输入管理员口令 `e2vPsv8$` 及卸载码 `e2vPsv8$` 完成操作。&#10;&#10;4. **方式三：通过控制面板卸载**  &#10;   - 按 `Win + R` 键，输入 `control` 并回车打开控制面板。  &#10;   - 点击**卸载程序**（或“程序和功能”）。  &#10;   - 在列表中找到“安全助手”，双击进行卸载。  &#10;   - 根据提示输入相应的密码完成流程。&#10;&#10;**💡 提示**: &#10;- 如果您计划安装新的零信任工具，建议先彻底卸载旧版安全助手，若无旧版本可直接覆盖安装。&#10;- 若遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**安装零信任**，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备与卸载（如已安装旧版）**  &#10;   如果您电脑上已安装“安全助手”，请先将其卸载，再安装零信任。&#10;   - **获取密码**：管理员口令和卸载码均为 `e2vPsv8$`。&#10;   - **卸载方式**：&#10;     - *方式一*：右键点击安全助手图标 -&gt; 进入特权模式（输入密码）-&gt; 在路径 `C:\Windows\LVUAAgentInstBaseRoot` 下找到文件运行卸载 -&gt; 输入卸载码 `e2vPsv8$` 确认。&#10;     - *方式二*：Win10系统可点击左下角搜索“UniAccess安全助手” -&gt; 打开文件位置 -&gt; 找到卸载程序运行并输入密码。&#10;   - *注*：如果没有安装安全助手，可直接进行下一步覆盖安装。&#10;&#10;2. **下载并启动安装包**  &#10;   - 访问下载链接获取 Windows 版本安装包：`https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;   - 双击打开安装包，在弹出的用户账户控制窗口中点击&quot;**是**&quot;。&#10;&#10;3. **同意协议并选择位置**  &#10;   - 阅读协议后，点击&quot;**我同意**&quot;。&#10;   - 选择安装位置（默认即可），点击&quot;**安装**&quot;按钮。&#10;&#10;4. **完成安装与登录**  &#10;   - 等待安装进度条完成。&#10;   - 安装完成后，确保勾选“运行零信任”，此时桌面会出现“零信任”图标。&#10;   - 打开零信任客户端，使用手机扫码登录。&#10;   - *特殊情况*：如果首次安装提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认后扫码即可。&#10;&#10;**💡 提示**: &#10;- 安装过程中请保持网络连接畅通。&#10;- 如果安装后未显示图标，可能是与 IOA 软件冲突，需前往 `C:\Program Files (x86)\TrustCyberLink` 目录手动运行 `TrustCyberLink.exe`。&#10;- 登录后请勿随意退出零信任客户端，否则可能导致无法访问内部系统（如 TMS、EVIP 等）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于处理零信任控制器异常，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   当打开零信任提示“连接控制器失败”时，请在客户端界面选择“切换控制器”，并将地址手动修改为：**124.71.208.207**。&#10;&#10;2. **重置并重新输入控制器**  &#10;   如果切换地址后问题仍未解决，请选择“重置控制器”功能，然后再次手动输入正确的控制器地址：**124.71.208.207**（或域名 `sec.zy.com`），确认后进行扫码登录。&#10;&#10;3. **检查软件冲突与版本**  &#10;   - 若提示“开启私网DNS失败”，可能是软件版本过旧或存在冲突。请联系IT帮助台获取最新安装包进行覆盖安装。&#10;   - 确保电脑上已卸载不再使用的IOA软件，避免网络策略冲突。&#10;&#10;**💡 提示**: &#10;- 标准控制器地址为 `124.71.208.207`，请确保输入无误。&#10;- 操作前建议先退出零信任客户端，再执行重置或切换操作。&#10;- 如遇到其他登录异常（如认证失败、应用空白等），可尝试退出后重新扫码登录。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于查看零信任控制器地址，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认标准控制器地址**  &#10;   根据官方配置指引，零信任客户端的标准控制器地址为：**124.71.208.207**。  &#10;   *注：部分旧文档或特定场景下也可能使用域名 `sec.zy.com`，但推荐优先使用 IP 地址。*&#10;&#10;2. **在客户端中查看或修改（如已安装）**  &#10;   - 打开桌面上的“零信任”图标启动软件。&#10;   - 如果软件未自动连接，通常会弹出提示要求输入控制器地址。&#10;   - 若需手动切换，可在设置界面选择“控制器切换”，输入上述地址 `124.71.208.207` 并确认。&#10;&#10;3. **参考安装指引中的默认值**  &#10;   在安装过程中（步骤7），系统会提示输入控制器地址，此时应直接输入 `124.71.208.207` 或 `sec.zy.com`。&#10;&#10;**💡 提示**: &#10;- 如果您遇到“连接控制器失败”的报错，请尝试切换到 `124.71.208.207` 地址。&#10;- 如果切换后仍无法解决，可尝试重置控制器设置后重新输入该地址。&#10;- 确保网络连接正常，且未被第三方杀毒软件拦截。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于通过企业微信修改263邮箱密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **进入IT服务台**  &#10;   打开【企业微信】，点击底部菜单栏的【工作台】，找到并点击【IT服务台】。&#10;&#10;2. **选择密码重置功能**  &#10;   在IT服务台页面中，点击【更多功能】，然后选择【邮箱密码重置】。&#10;&#10;3. **按指引完成修改**  &#10;   根据页面提示的步骤进行验证（如短信验证码等），输入新密码并完成修改。&#10;   &gt; **注意**：新密码需包含大小写字母、数字和符号，长度不小于8位，且不能使用连续字符或简单密码。&#10;&#10;4. **重新绑定企业微信（如需）**  &#10;   如果之前已绑定企业微信，密码修改后可能需要重新登录绑定：&#10;   - 返回企业微信【工作台】，点击【263企业邮箱】；&#10;   - 输入新的邮箱账号和密码，完成重新绑定。&#10;&#10;**💡 提示**: &#10;- 若遇到“用户邮箱状态异常”提示，请先完成上述密码重置步骤，再尝试重新绑定。&#10;- 如旧手机号无法接收验证码，需在OA系统发起【账户/权限申请】流程变更绑定手机。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于安装悦智学打印驱动（插件），具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开火狐浏览器并进入配置页面**  &#10;   启动火狐浏览器，在地址栏输入 `about:config` 并回车。&#10;&#10;2. **搜索安全协议设置**  &#10;   在弹出的搜索框中输入 `security.tls.version.min`。&#10;   *注：此步骤是为了调整浏览器的安全策略，以便允许访问本地打印机服务。*&#10;&#10;3. **执行插件安装**  &#10;   完成上述设置后，点击 TMS（或相关安装链接）执行安装程序。&#10;   *注意：此时浏览器可能会弹出“面临潜在的安全风险”的警告提示，这是因为 Firefox 检测到对 localhost 的访问。请确认无误后选择继续访问以完成安装。*&#10;&#10;**💡 提示**: &#10;- 该指引主要针对**火狐浏览器**环境。&#10;- 安装过程中出现的本地安全风险警告属于正常现象，是因为需要连接本地打印机服务，请放心操作。&#10;- 安装完成后，即可在备课界面通过【课堂资料】-【预览】-【打印】功能使用打印服务。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何使用零信任系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **安装零信任客户端**&#10;   - 双击打开安装包，点击“是”确认。&#10;   - 勾选“我同意”，选择默认安装位置（或自定义），点击“安装”。&#10;   - 等待安装完成，确保勾选“运行零信任”，此时桌面会出现零信任图标。&#10;&#10;2. **配置控制器地址（如需要）**&#10;   - 首次启动时若提示输入控制器地址，请输入：`sec.zy.com` 或 `124.71.208.207`。&#10;   - 点击确认后进入登录界面。&#10;&#10;3. **登录零信任系统**&#10;   - 打开零信任客户端，选择“扫码登录”方式。&#10;   - 使用企业微信或指定扫码工具扫描二维码完成认证。&#10;   - 若遇到“不合法的用户名”、“会话过期”或“认证失败”等提示，请返回上一级，选择“快捷方式登录”。&#10;&#10;4. **访问内部应用**&#10;   - 登录成功后，通过浏览器访问公司内部系统。&#10;   - 若出现“无法访问此网页”或&quot;403 Forbidden”错误：&#10;     - 尝试关闭浏览器后重新打开；&#10;     - 在零信任客户端中点击“刷新策略”；&#10;     - 如仍未解决，可退出零信任并重新扫码登录；&#10;     - 建议更换为 Google Chrome 或 Firefox 浏览器尝试访问。&#10;&#10;5. **处理常见异常（可选）**&#10;   - 若退出零信任后无法访问外网：清除本地 DNS 设置（将 `127.0.0.1` 改为自动获取）。&#10;   - 若仅能登录企微/微信但无法打开网页：检查并修改 Internet 代理设置。&#10;   - 若与 IOA 软件冲突导致网络异常：卸载 IOA 并重启电脑。&#10;   - 若开机弹窗警告或启动慢：卸载第三方杀毒软件（如 360、火绒等）并禁用非必要启动项。&#10;&#10;**💡 提示**: &#10;- 登录前请确保网络连接正常；&#10;- 如遇控制器连接失败，可手动切换或重置控制器地址为 `124.71.208.207`；&#10;- Mac 用户若遇 JavaScript 错误，可在终端添加 `127.0.0.1 localhost` 到 `/etc/hosts` 文件；&#10;- 卸载零信任前请先退出程序，Mac 用户还需清理 DNS 设置。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何用浏览器查看监控，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认系统环境**  &#10;   确保您的电脑操作系统为 **Windows 10 或更高版本**。&#10;&#10;2. **开启 Edge 浏览器的 IE 模式**  &#10;   - 打开 Edge 浏览器，点击右上角的 **三个点 (···)**，选择 **“设置”**。&#10;   - 在搜索框中输入 **&quot;Explorer&quot;**。&#10;   - 向下滚动找到 **“允许在 Internet Explorer 模式下重新加载网站”** 选项，将其设置为 **“允许”**。&#10;   - 重启浏览器后，右上角菜单中会出现 **“在 Internet Explorer 模式下重新加载”** 选项。&#10;&#10;3. **访问监控地址**  &#10;   - 在浏览器地址栏输入监控 IP 地址：**192.168.0.X**（X 的范围通常为 5~10）。&#10;   - 进入登录界面后，先点击右上角的 **三个点**，选择 **“在 Internet Explorer 模式下重新加载”**。&#10;&#10;4. **登录监控系统**  &#10;   根据需求选择账号登录：&#10;   - **有回放功能**：用户名 `userxq`，密码 `345110xq`&#10;   - **无回放功能**：用户名 `user`，密码 `345110jk`&#10;&#10;5. **安装必要插件**  &#10;   首次使用时，系统会提示下载插件，请根据页面提示完成下载和安装。&#10;&#10;6. **开启兼容性设置**  &#10;   登录后，点击左上角的 **【e】** 标志，开启 **“兼容性”** 并勾选 **“下次在 IE 模式下打开”**，以便后续直接访问。&#10;&#10;**💡 提示**: &#10;- 如果无法查看回放，请检查是否使用了带有回放权限的账号（如 `userxq`）。&#10;- 如遇其他问题，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Edge浏览器查看监控，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **开启IE模式设置**  &#10;   打开Edge浏览器，点击右上角的“三个点”图标，选择【设置】。在搜索框中输入“Explorer”，向下滚动找到“允许在Internet Explorer模式下重新加载网站(IE模式)”，将其设置为“允许”。此时，右上角菜单中会出现“在Internet Explorer模式下重新加载”选项。&#10;&#10;2. **访问监控地址并切换模式**  &#10;   在浏览器地址栏输入监控IP地址（格式为 `192.168.0.X`，其中X通常为5~10）。进入登录界面后，再次点击右上角的“三个点”，选择“在Internet Explorer模式下重新加载”。&#10;&#10;3. **登录与插件安装**  &#10;   页面刷新后，输入账号密码进行登录：&#10;   - 普通用户1（有回放功能）：账号 `userxq`，密码 `345110xq`&#10;   - 普通用户2（无回放功能）：账号 `user`，密码 `345110jk`  &#10;   首次使用时，系统会提示下载插件，请根据提示完成下载和安装。&#10;&#10;4. **启用兼容性模式**  &#10;   登录成功后，点击左上角的【e】标志，开启“兼容性”选项，并勾选“下次在IE模式下打开”，以便后续直接以兼容模式访问。&#10;&#10;**💡 提示**: &#10;- 确保电脑系统为Win10及以上版本。&#10;- 若遇到无法下载插件的问题，可尝试关闭Edge浏览器的SmartScreen筛选器（路径：设置 &gt; 高级设置 &gt; 关闭“启用SmartScreen筛选器”），或更换为谷歌浏览器、火狐浏览器等替代方案。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决263邮箱密码错误被锁问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信重置密码**  &#10;   登录【企业微信】，点击【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】。按照页面提示的步骤完成新密码的修改。&#10;   *注意：根据安全规定，密码需包含大小写字母、数字和符号，长度不小于8位，且不能使用连续字符或简单密码。*&#10;&#10;2. **重新绑定企业微信（如适用）**  &#10;   如果之前已绑定企业微信，在重置密码后，需要重新进行绑定才能正常使用。&#10;   路径：登录【企业微信】&gt;【工作台】&gt;【263企业邮箱】，输入新的邮箱账号和密码完成绑定。&#10;&#10;3. **更新客户端密码（如使用Outlook/Foxmail/Mac Mail等）**  &#10;   如果您在电脑客户端（如Outlook、Foxmail或Macbook邮件）中使用了旧密码，需要在客户端设置中同步更新为新密码，否则仍会提示登录失败。&#10;   *参考指引：Outlook或Macbook邮件配置步骤可参考相关图文指引，确保服务器地址（IMAP+SMTP）正确。*&#10;&#10;4. **特殊情况处理**  &#10;   如果提示“用户邮箱状态异常”或无法通过上述方式解锁，请先执行第1步重置密码，再尝试重新登录。若问题依旧，建议联系IT帮助台或在OA系统（http://oa.zy.com）上提交IT报障单寻求进一步支持。&#10;&#10;**💡 提示**: &#10;- 263企业邮箱要求每90天修改一次密码，首次登录后也需立即修改，否则账号可能被停用。&#10;- 请勿点击可疑邮件中的链接或下载附件，以防钓鱼攻击导致账号异常。&#10;- 如遇手机号变更无法接收验证码，需在OA系统发起“账户/权限申请”流程变更绑定手机。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重新绑定263邮箱和企业微信，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **重置邮箱密码（如需要）**  &#10;   如果之前因密码问题导致解绑，或提示“用户邮箱状态异常”，请先重置密码：  &#10;   - 登录企业微信 → 点击【工作台】→【IT服务台】→【更多功能】→【邮箱密码重置】。  &#10;   - 按提示完成密码重置。&#10;&#10;2. **在企业微信中重新绑定263邮箱**  &#10;   - 打开企业微信，进入【工作台】。  &#10;   - 找到并点击【263企业邮箱】应用图标。  &#10;   - 输入您的263邮箱账号和**新设置的密码**。  &#10;   - 点击确认完成绑定。&#10;&#10;**💡 提示**: &#10;- 重置密码后，必须重新在企业微信中绑定才能正常使用。&#10;- 确保输入的邮箱地址和密码准确无误，密码需包含大小写字母、数字及符号，长度不少于8位。&#10;- 如仍无法绑定，请检查网络环境或联系IT帮助台协助处理。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何打开263邮箱链接，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问网页版登录地址**  &#10;   在电脑或手机的浏览器中复制并打开以下网址：  &#10;   `https://www.263.net`&#10;&#10;2. **输入账号密码登录**  &#10;   - 点击页面上的【登录】按钮。&#10;   - 输入您的企业邮箱账号和密码。&#10;   - *注：如果是新用户初次登录，系统会提示您必须关联手机号码（需输入手机号和短信验证码）才能完成登录。*&#10;&#10;3. **处理特殊情况**  &#10;   - **忘记密码**：如果不知道密码，请先在企业微信中通过【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】进行重置，然后再尝试登录。&#10;   - **状态异常**：如果登录后提示“用户邮箱状态异常”，同样需要先执行上述密码重置步骤，并重新绑定企业微信。&#10;&#10;**💡 提示**: &#10;- 如果您需要在Outlook、Foxmail或Mac客户端使用，请前往相关配置指引文档查看服务器地址设置（建议使用IMAP+SMTP组合）。&#10;- 首次登录或每90天需要修改一次密码以符合安全规范。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决企业邮箱密码错误，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置密码**  &#10;   这是最便捷的修改方式。请登录**企业微信**，依次点击：【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】，按照页面指引完成新密码设置。&#10;&#10;2. **通过网页端重置密码（已绑定手机）**  &#10;   如果您的邮箱已绑定手机号，可以直接访问网址 `https://mm.263.com/wm2e/website/jsp/resetPassword.jsp` 进行密码重置。&#10;&#10;3. **处理“用户邮箱状态异常”提示**  &#10;   如果登录时提示“用户邮箱状态异常”，通常是因为密码过期或需要重新验证。请先执行**步骤1**进行密码重置，重置完成后，需重新在企业微信中绑定邮箱才能正常使用。&#10;&#10;4. **同步更新客户端密码**  &#10;   如果您在电脑（如Outlook、Foxmail）或手机上配置了邮件客户端，修改密码后，请务必在这些客户端中同步更新新密码，否则无法收发邮件。&#10;&#10;5. **注意密码规则**  &#10;   设置新密码时请确保符合以下要求：&#10;   - 长度不小于8位&#10;   - 必须包含大写字母、小写字母、数字和符号&#10;   - 不能使用连续字符或简单密码&#10;&#10;**💡 提示**: &#10;- 根据安全管理要求，首次使用及每90天需强制修改一次密码，若特殊邮箱90天内未修改，账号将被停用。&#10;- 修改密码并重置后，如果之前绑定了企业微信，可能需要重新输入新密码进行绑定。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何用Edge浏览器查看监控，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **开启IE模式**  &#10;   打开Edge浏览器，点击右上角的三个点（设置），在搜索框输入“Explorer”，找到并允许“在Internet Explorer模式下重新加载网站”。&#10;&#10;2. **访问监控地址**  &#10;   在浏览器地址栏输入监控IP地址（格式为 `192.168.0.X`，X通常为5~10），进入登录界面。&#10;&#10;3. **切换至IE模式**  &#10;   在登录页面右上角点击三个点，选择“在Internet Explorer模式下重新加载”；首次使用可能会提示下载插件，按提示完成安装即可。&#10;&#10;4. **登录监控系统**  &#10;   根据需求选择账号登录：&#10;   - 有回放功能：用户名 `userxq`，密码 `345110xq`&#10;   - 无回放功能：用户名 `user`，密码 `345110jk`&#10;&#10;5. **启用兼容性设置（可选）**  &#10;   左上角点击【e】标志，开启“兼容性”并勾选“下次在IE模式下打开”，以便后续自动以IE模式访问。&#10;&#10;**💡 提示**: 如遇问题，可联系IT帮助台或在OA系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于清理磁盘空间，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带工具清理 (C盘)**  &#10;   按下键盘上的 `Win` 键，搜索并打开“磁盘清理”工具，按照提示选择需要清理的文件类型进行删除。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信客户端 -&gt; 点击左下角菜单 -&gt; 选择“设置” -&gt; “文件管理” -&gt; 点击“文件管理”按钮进入文件夹 -&gt; 点击“更改”，将存储路径修改为 C 盘以外的其他盘符（如 D 盘），以释放 C 盘空间。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   打开企业微信客户端 -&gt; 点击左下角菜单 -&gt; 选择“设置” -&gt; “存储管理”，根据指引将数据存储位置迁移至其他盘符。&#10;&#10;4. **手动删除临时文件**  &#10;   按下 `Win + R` 键，在运行框中输入 `%temp%` 并回车，选中文件夹内所有文件并删除（跳过正在使用的文件）。&#10;&#10;5. **使用一体机专用清理工具 (D盘)**  &#10;   如果您使用的是教学一体机：&#10;   - 打开“此电脑”并进入 D 盘；&#10;   - 找到名为“清理D盘.bat”的文件，双击运行；&#10;   - **注意**：运行过程中请勿点击黑框，以免停止运行；&#10;   - 看到“垃圾文件清理成功”提示后，按任意键退出。&#10;&#10;6. **清理手机端聊天记录 (释放云端/本地关联空间)**  &#10;   打开手机端企业微信 -&gt; 左上角“三”图标 -&gt; 右下角“设置” -&gt; “通用” -&gt; “存储空间” -&gt; “清理”，可选择特定群聊或全选进行清理。&#10;&#10;**💡 提示**: &#10;- 在进行重要数据迁移或删除前，建议先备份重要文件。&#10;- 清理临时文件时，如果某些文件无法删除，通常是因为它们正在被程序使用，可忽略或重启电脑后再试。&#10;- 如操作中遇到其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何进行邮箱扩容，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **登录邮箱并检查条件**  &#10;   首先登录您的263邮箱。请注意，只有当您的剩余信封数量**不足2000封**时，系统才会允许您进行扩容申请。&#10;&#10;2. **找到扩容入口**  &#10;   在邮箱主界面中，寻找并点击标有&quot;**扩容**&quot;的按钮或选项。&#10;&#10;3. **提交申请**  &#10;   点击后按照页面提示完成扩容申请流程。&#10;&#10;**💡 提示**: &#10;- 如果在使用过程中遇到其他问题，可以联系IT帮助台，或在OA系统上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;- 确保您的邮箱状态正常且满足“信封不足2000封”的条件，否则可能无法看到扩容入口。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于更换教学一体机壁纸,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **准备壁纸图片**  &#10;   确保您的新壁纸图片格式为 **jpg**。如果是其他格式（如png），请先修改文件扩展名：&#10;   - 在文件夹中点击“查看”，勾选“文件扩展名”。&#10;   - 将文件名后缀从 `.png` 等改为 `.jpg`，并回车确认。&#10;   - 将图片重命名为 **`1.jpg`**。&#10;&#10;2. **备份当前壁纸**  &#10;   进入电脑 **D盘** 下的 **“壁纸”** 文件夹。&#10;   - 找到现有的 `1.jpg` 文件。&#10;   - 将其重命名为 **`3.jpg`**（此步骤是为了保留旧壁纸，以便日后需要时切换回来）。&#10;&#10;3. **设置新壁纸**  &#10;   - 将准备好的新图片（已命名为 `1.jpg`）复制并粘贴到 D盘的“壁纸”文件夹中。&#10;   - 返回教学一体机桌面，**等待约1分钟**。&#10;   - 当桌面显示为您新上传的图片时，即表示更换成功。&#10;&#10;**💡 提示**: &#10;- 系统会自动检测“壁纸”文件夹中的 `1.jpg` 进行更新，请务必确保文件名准确无误。&#10;- 如果在使用过程中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于零信任登录失败问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **尝试切换登录方式（快捷登录）**  &#10;   如果扫码登录提示“认证失败”、“不合法的状态”或“会话已过期”，请返回上一级界面，去掉用户名输入框，选择**快捷登录方式**。&#10;   *   *适用场景*：扫码认证失败、提示不合法状态、会话过期。&#10;&#10;2. **检查并解决软件冲突（IOA/杀毒软件）**  &#10;   *   **卸载旧版IOA**：确认电脑上是否安装了旧的IOA客户端。如果有，建议**卸载**IOA（因已不再使用），然后重新扫码登录零信任。&#10;   *   **清理第三方杀毒软件**：如果开机慢或弹窗干扰，请卸载360安全卫士、金山毒霸、火绒安全、鲁大师等第三方杀毒软件，并禁用不必要的开机启动项。&#10;&#10;3. **重置控制器地址**  &#10;   如果提示“连接控制器失败”或无法启动：&#10;   *   在零信任客户端中选择**切换控制器**，手动输入地址：`124.71.208.207`。&#10;   *   若切换后仍无效，可选择**重置控制器**，再次输入上述地址。&#10;&#10;4. **修复系统环境（针对Mac用户）**  &#10;   *   **JavaScript错误**：打开终端，执行 `sudo vi /etc/hosts`，添加一行 `127.0.0.1 localhost` 保存退出。&#10;   *   **DNS设置**：如果提示“开启私网DNS失败”，请联系IT帮助台获取最新版本安装包覆盖安装；或检查本机网络设置，确保未强制绑定错误的DNS（如127.0.0.1）。&#10;&#10;5. **重新安装客户端**  &#10;   如果安装完成后未显示“零信任”图标，或提示找不到文件（如UAADataCenter.dll）：&#10;   *   尝试重新运行安装程序进行覆盖安装。&#10;   *   对于Windows 10用户，可尝试直接去安装目录 `C:\Program Files (x86)\TrustCyberLink` 下打开 `TrustCyberLink.exe`。&#10;&#10;**💡 提示**: &#10;*   登录成功后，请勿随意退出零信任客户端，否则可能导致内网应用无法访问。&#10;*   如果是兼职老师遇到应用列表空白，通常是组织架构同步问题，需联系零信任管理员人工调整分组。&#10;*   部分浏览器（如Safari、火狐）可能报403错误，建议优先使用**Google浏览器**访问应用。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决打印机脱机无法打印问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并取消 SNMP 状态设置**  &#10;   如果打印机显示“脱机”，通常是因为启用了 SNMP 状态检测。请按以下步骤操作：&#10;   - 打开“控制面板” &gt; “硬件和设备”（或“设备和打印机”）。&#10;   - 找到对应的打印机，右键点击选择“打印机属性”。&#10;   - 进入“端口”选项卡，找到当前使用的 IP 地址端口。&#10;   - 取消勾选“启用 SNMP 状态”或类似选项（不同系统版本可能略有差异）。&#10;   - 点击“应用”并“确定”保存设置。&#10;&#10;2. **确认网络连接正常**  &#10;   - 确保打印机已连接网络，且网线或 Wi-Fi 信号稳定。&#10;   - 可尝试重启打印机和电脑，重新建立连接。&#10;&#10;3. **验证打印机状态**  &#10;   - 在“设备和打印机”中查看该打印机是否仍显示为“脱机”。&#10;   - 若仍为脱机，可尝试右键点击打印机，选择“查看现在正在打印什么”，然后取消所有任务，再重新添加测试页。&#10;&#10;**💡 提示**: 如上述方法无效，可能是驱动或系统策略问题，建议联系 IT 帮助台或在 OA 系统（http://oa.zy.com）提交报障单获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载零信任最新安装包，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **Windows 用户下载**  &#10;   直接访问以下链接下载 Windows 版本安装包：  &#10;   https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  &#10;&#10;2. **Mac 用户下载**  &#10;   直接访问以下链接下载 Mac 版本安装包：  &#10;   https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg  &#10;&#10;3. **获取更新版本（如需要）**  &#10;   如果上述链接不是您需要的最新版本，请通过**企业微信联系 IT 帮助台**获取最新版安装包。&#10;&#10;**💡 提示**: &#10;- 安装前建议先卸载旧版“安全助手”（如有），再安装零信任工具。&#10;- 若安装过程中遇到权限问题（如 Mac 提权密码错误），请检查系统隐私与安全性设置中是否已授权零信任程序。"/>
+        <filter val="好的!关于登录绩效人才系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业门户登录（推荐）**&#10;   - 打开浏览器（推荐使用谷歌 Chrome 浏览器）。&#10;   - 访问企业门户网址：`https://ssoin.zy.com/ogin`。&#10;   - 登录后，在首页导航栏找到并点击 **“绩效人才系统”**。&#10;   - 进入系统后，选择 **“我的学习”** 或相关功能模块即可开始使用。&#10;&#10;2. **通过 Italent 系统直接登录**&#10;   - 访问 Italent 系统网址：`https://www.italent.cn/Login`。&#10;   - **账号**：输入您的企业邮箱账号。&#10;   - **密码**：如果忘记密码，请点击“忘记密码”进行重新设置。&#10;&#10;3. **通过移动端快捷入口**&#10;   - 关注企业微信或查收企业邮箱，寻找由“绩效与学习平台”自动发送的学习通知。&#10;   - 点击通知中的链接，可直接跳转至系统进行学习或操作。&#10;&#10;**💡 提示**: &#10;- 建议优先使用 **Chrome 浏览器** 访问，以获得最佳兼容性体验。&#10;- 如果是新入职员工，首次登录可能需要先完成年度绩效计划的制定，如有问题可咨询 HRBP。&#10;- 确保您已激活企业邮箱账号，这是登录系统的唯一凭证。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于苹果电脑零信任系统加载转圈问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并开启“完全磁盘访问权限”**  &#10;   此问题通常出现在 Mac (Intel x86) 设备上。请进入 **系统设置 &gt; 隐私与安全性 &gt; 完全磁盘访问权限**，在右侧列表中找到并勾选允许以下两个进程：&#10;   - `dvc-filemonitor-exe`&#10;   - `dvc-screen-exe`  &#10;   开启后，重新打开零信任客户端尝试登录。&#10;&#10;2. **检查“安全性与隐私”设置（针对安装或运行报错）**  &#10;   如果是在安装或运行阶段出现卡死，请进入 **系统设置 &gt; 隐私与安全性 &gt; 安全性**，确保已选择 **“任何来源”** 以允许未识别开发者的应用运行。&#10;&#10;3. **联系管理员处理权限问题**  &#10;   如果执行上述步骤后问题依旧存在，说明可能涉及更深层的权限配置问题。此时需要联系中后台安全对接群或零信任管理员进行人工排查和解决。&#10;&#10;**💡 提示**: &#10;- 操作前请确保您的 Mac 系统版本支持相关功能。&#10;- 修改权限设置后，建议重启一次零信任客户端或重启电脑以确保设置生效。&#10;- 如果是 Mac (ARM) 架构设备遇到类似“转圈圈”问题（如卡巴斯基系统扩展），需额外在“安全性与隐私”中允许&quot;Kaspersky Endpoint Security Daemon&quot;载入。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于登录监控系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用客户端软件登录 (推荐)**&#10;   - 打开监控客户端软件“iVMS-4200”。&#10;   - 在主菜单界面右侧点击“设备管理”，选择需要连接的监控设备。&#10;   - 点击设备旁边的“笔形状图标”进入编辑模式。&#10;   - 输入账号和密码：&#10;     - **若需查看回放**：用户名 `userxq`，密码 `345110xq`&#10;     - **仅查看实时画面**：用户名 `user`，密码 `345110jk`&#10;   - 保存后，当状态显示为“在线”即表示连接成功。&#10;&#10;2. **使用Edge浏览器网页登录**&#10;   - 打开Edge浏览器，点击右上角三个点，进入“设置”。&#10;   - 在搜索框输入“Explorer”，找到并开启“允许在Internet Explorer模式下重新加载网站”。&#10;   - 在地址栏输入监控IP地址（格式通常为 `192.168.0.X`，X范围一般为5~10）。&#10;   - 页面加载后，再次点击右上角三个点，选择“在Internet Explorer模式下重新加载”。&#10;   - 在弹出的登录界面中输入上述对应的账号密码即可登录。&#10;&#10;**💡 提示**: &#10;- 请注意区分账号权限，只有使用 `userxq` 账号才具备录像回放功能。&#10;- 如果是在新安装的监控设备上，建议先通过客户端将NTP服务器设置为 `ntp.aliyun.com` 以防止时间不同步。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重置263企业邮箱密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助重置（推荐）**  &#10;   打开【企业微信】，点击底部【工作台】 &gt; 【IT服务台】 &gt; 【更多功能】 &gt; 【邮箱密码重置】。按照页面提示输入相关信息并完成新密码设置。&#10;&#10;2. **通过网页端重置（需已绑定手机）**  &#10;   如果您之前已绑定手机号，可直接访问网址：`https://mm.263.com/wm2e/website/jsp/resetPassword.jsp`，按指引进行密码修改。&#10;&#10;3. **特殊情况处理（手机号已注销或无法接收验证码）**  &#10;   如果绑定的旧手机号码已注销或无法接收短信，请登录OA系统，发起流程：【发起流程】-【IT类】-【IT服务】-【账户/权限申请】。在“系统”中选择&quot;263企业邮箱”，并在“描述”中详细说明变更需求。&#10;&#10;4. **重置后重新绑定客户端**  &#10;   密码重置成功后，如果您使用企业微信、Outlook、Foxmail或Macbook邮件客户端，需要重新输入新密码进行绑定或更新配置，才能正常使用。&#10;&#10;**💡 提示**: &#10;*   **密码规则**：新密码长度需不小于8位，必须包含大写字母、小写字母、数字和符号，且不能使用连续字符或简单密码。&#10;*   **状态异常**：如果登录时提示“用户邮箱状态异常”，请先执行上述第1步进行密码重置，然后再尝试重新绑定。&#10;*   **寻求帮助**：如操作中遇到其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于更改企业邮箱密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信自助修改（推荐）**  &#10;   打开【企业微信】&gt; 点击【工作台】&gt; 选择【IT服务台】&gt; 点击【更多功能】&gt; 选择【邮箱密码重置】，按页面指引完成修改。&#10;&#10;2. **通过网页端修改（已绑定手机）**  &#10;   访问网址 `https://mm.263.com/wm2e/website/jsp/resetPassword.jsp`，输入相关信息后按提示重置密码。&#10;&#10;3. **同步客户端密码**  &#10;   如果您在电脑或手机上使用了 Foxmail、Outlook 等邮件客户端，修改密码后请务必在这些客户端中同步更新新密码，以免无法收发邮件。&#10;&#10;**💡 提示**: &#10;- 密码规则：需包含大小写字母、数字和符号，长度不小于8位，不能使用连续字符或简单密码。&#10;- 安全提醒：根据安全管理要求，首次登录及每90天需修改一次密码，否则账号可能被停用。&#10;- 若遇到“用户邮箱状态异常”提示，请先执行步骤1进行密码重置，再重新绑定企业微信。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于Windows系统安装京瓷打印机驱动，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并解压驱动包**  &#10;   访问“京瓷打印机驱动下载”页面，将对应的驱动包下载到电脑硬盘上。下载完成后，右键点击压缩包选择“解压”到指定文件夹。&#10;&#10;2. **收集必要信息**  &#10;   在安装前，请确认打印机的**IP地址**和**型号**（部分共用打印机还需准备部门密码）。&#10;   - *查询IP地址*：参考相关图示或联系管理员获取。&#10;   - *查询型号*：查看打印机机身标签或通过打印机面板菜单查询。&#10;&#10;3. **运行安装程序**  &#10;   进入解压后的文件夹，双击运行 `Setup.exe` 文件启动安装向导。&#10;&#10;4. **自定义安装配置**  &#10;   - 接受许可协议。&#10;   - 选择“**自定义安装**”模式。&#10;   - 根据实际收集到的**打印机型号**和**IP地址**填写相应信息。&#10;   - 勾选需要安装的组件（如添加打印机驱动、升级组件等）。&#10;&#10;5. **完成安装**  &#10;   按照提示完成剩余步骤，直到显示“打印机安装完成”。&#10;&#10;6. **后续设置（可选）**  &#10;   - **修改名称与双面打印**：进入“控制面板” &gt; “硬件和设备”，右击打印机选择“属性”，可修改名称并设置双面打印功能。&#10;   - **解决脱机问题**：若打印机显示脱机，需在设置中取消“SNMP状态检测”。&#10;   - **添加部门ID**：如需使用部门代码，请在打印机属性中添加相应的部门ID。&#10;&#10;**💡 提示**: &#10;- 安装过程中请务必确保网络连接正常，以便正确识别打印机IP。&#10;- 如遇其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决零信任控制器无法连接问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，找到控制器设置选项，将控制器地址手动修改为：**124.71.208.207**。这是推荐的官方最佳设置地址。&#10;&#10;2. **重置并重新输入控制器**  &#10;   如果仅切换地址后问题依旧，请尝试在客户端中选择“重置控制器”功能，清除旧配置后，再次手动输入地址 **124.71.208.207** 并确认保存。&#10;&#10;3. **检查软件冲突（IOA）**  &#10;   如果上述步骤无效，请检查电脑是否安装了已停用的 **IOA** 软件。如果有，请将其卸载并重启电脑，因为 IOA 可能会与零信任客户端产生冲突导致连接失败。&#10;&#10;4. **重新扫码登录**  &#10;   完成上述设置后，退出当前零信任客户端，重新启动并尝试通过企业微信或微信扫码进行登录，以获取最新的网络策略。&#10;&#10;**💡 提示**: &#10;- 确保您的网络连接正常，且未开启可能拦截连接的第三方杀毒软件（如360、火绒等）。&#10;- 如果是 Mac 用户遇到 JavaScript 错误导致无法启动，可能需要先修复 hosts 文件（添加 `127.0.0.1 localhost`），但这通常针对启动报错而非单纯的控制器连接失败。&#10;- 若问题仍未解决，建议联系 IT 帮助台获取最新版本的安装包进行覆盖安装。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Mac上安装零信任，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **获取并运行安装包**&#10;   下载零信任客户端安装包（通常由安全部门提供），双击打开。&#10;   *注意：如果是Mac (Intel) 机型，若提示报错，需先去“系统设置”&gt;“隐私与安全性”&gt;“安全性”，选择“允许来自任何来源”。*&#10;&#10;2. **确认安装权限**&#10;   在安装过程中，系统可能会弹出安全提示。&#10;   *针对Mac (ARM) 机型：如果安装卡巴斯基组件时提示“系统扩展程序”转圈，需去“设置”&gt;“安全性与隐私”，允许“Kaspersky Endpoint Security Daemon”的系统软件加载。*&#10;   *针对Mac (Intel x86) 机型：如果登录一直转圈，需在“隐私与安全性”&gt;“完全磁盘访问权限”中，允许 `dvc-filemonitor-exe` 和 `dvc-screen-exe`。*&#10;&#10;3. **完成安装并启动**&#10;   等待安装进度条完成。安装结束后，默认会自动勾选“运行零信任”，此时桌面会出现零信任图标。&#10;&#10;4. **扫码登录**&#10;   打开桌面上的零信任图标，使用企业微信或指定二维码进行扫码登录。&#10;   *提示：如果首次安装提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认后扫码即可。*&#10;&#10;5. **检查网络配置（如未自动生效）**&#10;   如果登录后无法访问内部系统，请检查网络设置：&#10;   - 确保零信任客户端处于**运行状态**（不要退出）。&#10;   - 检查DNS设置：进入“系统设置”&gt;“网络”，查看DNS是否包含 `127.0.0.1`。如果没有，可能需要手动添加；如果之前有残留的 `127.0.0.1` 导致问题，请将其删除保存。&#10;   - 检查Hosts文件：打开终端，输入 `sudo vi /etc/hosts`，确认是否存在 `127.0.0.1 localhost` 记录，若无则需手动添加。&#10;&#10;**💡 提示**: &#10;- 安装前请确保电脑C盘（Windows）或对应磁盘空间充足，避免因空间不足导致安装失败。&#10;- 如果安装后不显示图标，可能是与IOA软件冲突，建议重新安装或联系管理员。&#10;- 使用过程中请勿随意退出零信任客户端，否则将无法访问内部系统。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于263邮箱无法接收验证码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **提交IT报障单申报故障**  &#10;   由于系统可能将您的IP列入黑名单或存在其他网络限制，需通过OA系统发起流程解决。&#10;   - 登录 **OA系统**。&#10;   - 点击 **【发起流程】** &gt; **【IT报障/预约服务单】**。&#10;   - 在 **【服务/故障描述】** 栏中按以下格式填写信息：&#10;     `263邮箱收不到验证码 手机：[您的手机号码] 邮箱账号：[您的邮箱地址] 登陆时间：[例如10:00~10:30]`&#10;   - 提交后等待IT部门处理。&#10;&#10;2. **检查是否因IP被封锁导致**  &#10;   如果登录时提示“IP地址在黑名单”，同样需要提交上述IT报障单，并在描述中注明：&#10;   `263邮箱黑名单IP：[您的IP地址] 邮箱账号：[您的邮箱地址]`&#10;&#10;**💡 提示**: &#10;- 请确保填写的手机号码和邮箱账号准确无误，以便IT人员快速定位问题。&#10;- 如果是新注册用户首次登录，请确认已在电脑网页端（https://www.263.net）完成手机号关联验证。&#10;- 若旧手机号已注销或无法接收短信，需走【账户/权限申请】流程变更绑定手机，而非直接报障。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何找回预数系统登录密码，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认登录方式**  &#10;   预数系统使用**员工通行证**进行登录。如果您修改过密码但忘记了，需要找回的是您的员工通行证密码。&#10;&#10;2. **访问密码找回页面**  &#10;   打开浏览器（推荐使用谷歌浏览器），访问以下地址：  &#10;   🔗 https://ucin.zy.com/forgot_password&#10;&#10;3. **按提示重置密码**  &#10;   在页面中输入您的员工账号信息，按照系统指引完成验证并设置新密码。&#10;&#10;4. **重新登录预数系统**  &#10;   密码重置成功后，返回预数系统登录页：  &#10;   🔗 https://jyys.zy.com/jyys/admin/login  &#10;   使用新的通行证密码登录即可。&#10;&#10;**💡 提示**: &#10;- 请确保使用**谷歌浏览器**访问，以获得最佳兼容性。&#10;- 如果无法通过上述链接找回密码，或遇到其他异常，请联系公司互联网管理中心或IT支持部门协助处理。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何下载并安装零信任，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载零信任安装包**&#10;   访问以下链接下载 Windows 版本的最新安装包：&#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;&#10;2. **（可选）卸载旧版安全助手**&#10;   *   **注意**：如果电脑上已安装“安全助手”，建议先卸载再安装零信任；如果没有安装，可直接进行下一步覆盖安装。&#10;   *   **方法一**：右键点击安全助手图标 -&gt; 进入特权模式 -&gt; 输入管理员口令 `e2vPsv8$` -&gt; 在路径 `C:\Windows\LVUAAgentInstBaseRoot` 下找到文件运行卸载 -&gt; 再次输入卸载码 `e2vPsv8$` 确认。&#10;   *   **方法二**：Win10系统可点击左下角搜索“UniAccess安全助手” -&gt; 打开文件位置 -&gt; 运行卸载程序并输入密码 `e2vPsv8$`。&#10;&#10;3. **运行安装程序**&#10;   *   双击下载的 `TrustCyberLink_PC_Setup_2.207.121.exe` 文件。&#10;   *   弹出用户账户控制窗口时，点击 **“是”**。&#10;   *   阅读协议后，点击 **“我同意”**。&#10;&#10;4. **选择安装位置并完成安装**&#10;   *   选择安装位置（默认即可），点击 **“安装”**。&#10;   *   等待安装进度条完成。&#10;   *   安装完成后，确保勾选 **“运行零信任”**，此时桌面会出现零信任图标。&#10;&#10;5. **登录使用**&#10;   *   打开桌面上的零信任图标。&#10;   *   如果是首次安装且提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认。&#10;   *   使用手机扫码登录，成功后即可通过浏览器访问内部系统。&#10;&#10;**💡 提示**: &#10;*   管理员口令和安全助手卸载码均为：`e2vPsv8$`。&#10;*   安装完成后请勿退出零信任客户端，否则可能导致无法访问内部系统（如TMS、EVIP等）。&#10;*   如果安装后未显示图标，可能是与IOA软件冲突，需前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 手动运行 `TrustCyberLink.exe`。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于电脑C盘空间不足的处理，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带磁盘清理工具**  &#10;   按下键盘上的 `Win` 键，在搜索框中输入“磁盘清理”并打开该功能，选择 C 盘进行扫描和清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信客户端，依次点击：设置 &gt; 文件管理 &gt; 文件管理（查看当前存储路径）&gt; 更改。将存储路径修改为 C 盘以外的其他盘符（如 D 盘或 E 盘），保存后重启微信，即可释放大量 C 盘空间。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   打开企业微信客户端，进入：设置 &gt; 存储管理，按照提示将聊天记录及文件存储位置迁移至非 C 盘分区。&#10;&#10;4. **手动删除临时文件**  &#10;   按下 `Win + R` 键，输入 `%temp%` 并回车，打开临时文件夹。全选所有文件（Ctrl+A），然后删除（Shift+Delete 可彻底删除），以清理系统产生的临时缓存。&#10;&#10;**💡 提示**: 在执行上述操作前，建议先备份重要数据；若操作过程中遇到权限问题或无法删除的文件，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）上提交报障单获取支持。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于**企业微信登录账号密码正确但无法登录的问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换至扫码登录**&#10;   如果输入账号密码后仍无法登录，建议尝试点击登录界面中的“切换到企业微信”选项，使用**企业微信扫码**进行登录。这是解决密码问题或系统验证异常的最有效方式。&#10;&#10;2. **检查手机号一致性**&#10;   确认您输入的登录手机号与入职登记时录入的手机号完全一致。如果手机号不一致，系统将无法匹配到对应的企业，导致登录失败。&#10;&#10;3. **检查微信安装状态（手机端）**&#10;   *   **iOS系统**：若未安装微信，仅显示手机号登录入口；若已安装，请确保网络正常。&#10;   *   **Android系统**：若未安装微信，会出现“微信登录”或“手机号登录”选项；若已安装但想切换手机号，可在登录界面点击右上角三个点，选择“手机号登录”。&#10;&#10;4. **联系管理员检查权限**&#10;   如果登录成功但看不到任何产品或数据，可能是权限未开通。请联系系统管理员，检查是否为您开通了当前业务模块、学科及产品类别的权限。&#10;&#10;**💡 提示**: &#10;*   如果是新成员加入，请确保已通过邀请链接确认加入，或手机号/身份证号已匹配到对应企业。&#10;*   若需更换绑定的微信号，请确保新微信已实名且与企业微信实名一致，且新旧微信均处于正常状态（无封号等）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何登录教学区监控系统，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用浏览器查看监控（推荐方式）**&#10;   - 确保电脑系统为 **Win10 及以上版本**。&#10;   - 打开 **Edge 浏览器**，点击右上角三个点，选择“设置”。&#10;   - 在搜索框输入 `Explorer`，找到并开启 **“允许在 Internet Explorer 模式下重新加载网站”**。&#10;   - 在地址栏输入监控 IP 地址（格式：`192.168.0.X`，X 通常为 5~10）。&#10;   - 进入登录界面后，再次点击右上角三个点，选择 **“在 Internet Explorer 模式下重新加载”**。&#10;   - 输入账号密码登录：&#10;     - **有回放功能账号**：用户名 `userxq`，密码 `345110xq`&#10;     - **无回放功能账号**：用户名 `user`，密码 `345110jk`&#10;&#10;2. **使用客户端软件查看监控（iVMS-4200）**&#10;   - 下载客户端：访问链接 [https://partners.hikvision.com/tools/tooldetail?id=599912121330368512](https://partners.hikvision.com/tools/tooldetail?id=599912121330368512) 下载 iVMS-4200 客户端。&#10;   - 安装时右键选择 **“以管理员身份运行”**，勾选协议，仅勾选 **“视频”** 功能，建议安装在非 C 盘。&#10;   - 启动软件后，点击右侧 **“设备管理”** -&gt; **“添加设备”**。&#10;   - 输入设备信息，并在账号设置中选择对应权限的账号：&#10;     - **有回放功能**：`userxq` / `345110xq`&#10;     - **无回放功能**：`user` / `345110jk`&#10;   - 连接成功后状态显示为 **“在线”** 即可开始预览或回放。&#10;&#10;**💡 提示**: &#10;- 若需查看历史回放，请务必使用 **userxq** 账号登录。&#10;- 如果客户端无法连接或画面异常，请检查 NTP 时间服务器是否设置为 `ntp.aliyun.com`。&#10;- 如遇其他问题，可联系 IT 帮助台或在 OA 系统（http://oa.zy.com）提交报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于如何使用263企业邮箱，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **初次登录与手机绑定**  &#10;   新用户首次使用必须在电脑网页端操作。请打开浏览器访问网址 `https://www.263.net`，点击【登录】输入您的邮箱账号和密码（若忘记密码可先重置）。登录后，系统会要求您输入手机号码并接收短信验证码，验证成功后即完成手机号关联。&#10;&#10;2. **日常网页登录**  &#10;   后续使用时，直接访问 `https://www.263.net`，输入账号和密码即可登录。如果提示“用户邮箱状态异常”，请先在企业微信中重置密码后再尝试登录。&#10;&#10;3. **移动端使用 (APP)**  &#10;   - **iPhone用户**：扫描指引图中的二维码下载263邮箱APP。&#10;   - **Android用户**：扫描指引图中的二维码下载263邮箱APP。&#10;   安装后使用您的企业邮箱账号和密码登录即可。&#10;&#10;4. **与企业微信集成**  &#10;   您可以直接在企业微信中使用邮箱：&#10;   - 打开企业微信 -&gt; 【工作台】 -&gt; 【263企业邮箱】。&#10;   - 输入邮箱账号和密码完成绑定。&#10;   - *注意*：如果您刚重置过密码，需要重新进行此绑定步骤才能正常使用。&#10;&#10;5. **客户端设置 (可选)**  &#10;   如需在Outlook或Foxmail等客户端使用，建议使用 **IMAP + SMTP** 组合配置服务器地址（具体地址请参考IT提供的附图），并确保密码符合安全规则（包含大小写字母、数字、符号，长度不小于8位）。&#10;&#10;**💡 提示**: &#10;- **密码安全**：根据安全管理要求，首次登录及每90天需修改一次密码，否则特殊邮箱可能会被停用。&#10;- **手机变更**：如果旧手机号已注销无法接收验证码，请登录OA系统发起【账户/权限申请】流程来变更捆绑的手机号。&#10;- **可疑邮件**：收到可疑邮件请勿点击链接或附件，请直接转发至 `sec-team@zy.com` 由安全专家处理。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于在Windows上安装监控软件，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载客户端**  &#10;   复制以下链接到浏览器打开并下载 iVMS-4200 客户端安装包：  &#10;   https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;2. **以管理员身份运行安装**  &#10;   找到下载的安装包（ivms-4200海康软件），**右键点击**选择【以管理员身份运行】，在弹出的提示框中选择【是】。&#10;&#10;3. **接受协议并开始安装**  &#10;   勾选【我接受许可证协议条款】，然后单击【下一步】按钮。&#10;&#10;4. **配置安装选项**  &#10;   - 在“请选择要安装的功能”界面，**只勾选【视频】**功能。&#10;   - 在“目标文件夹”处，建议切换到**非C盘**进行安装（例如D盘或E盘）。&#10;   - 确认无误后，单击【安装】按钮等待完成。&#10;&#10;5. **设置账号与添加设备**  &#10;   安装完成后，进入软件设置账号信息：&#10;   - **默认用户名**：`user`&#10;   - **默认密码**：`345110jk`&#10;   - **密保问题答案**：统一设置为 `1`&#10;   &#10;   随后进入【设备管理】—【设备】页面，根据需求添加录像机。若需查看回放功能，请确保使用有回放权限的账号（如：用户 `userxq`，密码 `345110xq`）。&#10;&#10;**💡 提示**: &#10;- 安装过程中如遇安全软件拦截，请暂时关闭360安全卫士、腾讯管家等软件后再试。&#10;- 登录软件时请注意区分“登录账号”与“监控回放账号”，若无法查看回放，请在设备管理中修改为有回放功能的账号。&#10;- 如有其他问题，可联系IT帮助台或在OA系统（http://oa.zy.com）填写报障单。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于解决打印机无法打印问题，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查并修改本地安全策略（针对多份打印失败）**&#10;   如果打印机无法进行多份打印，可能是用户账户控制设置导致。&#10;   - 打开“本地安全策略”。&#10;   - 依次选择：`安全设置` &gt; `本地策略` &gt; `安全选项`。&#10;   - 找到以下两项并设置为**禁用**：&#10;     - `用户账户控制：用于内置管理员账户的管理员批准`&#10;     - `用户账户控制：以管理员批准模式运行所有管理员`&#10;   - 设置完成后，**重启电脑**。&#10;&#10;2. **确认打印机状态与IP地址**&#10;   - **查看IP地址**：检查打印机机身标签或屏幕，确认IP地址是否正确。&#10;   - **处理脱机状态**：如果打印机显示“脱机”，需进入打印机属性，取消勾选&quot;SNMP状态检测”（Windows系统）。&#10;   - **检查物理连接**：若无法识别型号，请检查网线是否松动或打印机是否开机。&#10;&#10;3. **重新安装或更新驱动（如驱动异常）**&#10;   - **Windows系统**：&#10;     - 下载对应型号的京瓷驱动包。&#10;     - 解压后双击 `Setup.exe`，选择“自定义安装”，输入正确的IP地址和型号完成安装。&#10;   - **Mac系统**：&#10;     - 下载Mac专用驱动包，双击安装。&#10;     - 安装完成后务必**重启电脑**。&#10;     - 进入“系统偏好设置” &gt; “打印机与扫描仪”，点击“添加”，选择IP连接并输入打印机IP地址。&#10;&#10;4. **联系专业支持（硬件故障）**&#10;   如果上述软件操作无效，且遇到打印机无法开机、卡纸、硒鼓报错等硬件问题：&#10;   - 拨打报修电话或联系穗保客服。&#10;   - 或在OA系统（http://oa.zy.com）上填写IT报障单。&#10;&#10;**💡 提示**: &#10;- 在进行任何驱动安装前，请务必先收集好打印机的**IP地址**和**具体型号**。&#10;- Mac系统安装驱动后必须重启才能生效。&#10;- 如遇非网络或驱动类的硬件故障，请勿自行拆解，直接联系IT帮助台。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于重置通行证密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开企业微信**  &#10;   登录您的企业微信账号。&#10;&#10;2. **进入IT服务台**  &#10;   点击底部菜单栏的【工作台】，在应用列表中找到并点击【IT服务台】。&#10;&#10;3. **选择密码重置功能**  &#10;   在IT服务台页面中，点击【更多功能】，然后选择【通行证密码重置】。&#10;&#10;4. **按提示完成重置**  &#10;   根据页面指引输入相关信息（注意：通行证使用时不带@zy.com后缀），完成密码修改流程。&#10;&#10;**💡 提示**: &#10;- 通行证密码与邮箱密码不同，请勿混淆。&#10;- 如操作中遇到问题，可联系IT帮助台或在OA系统（http://oa.zy.com）上填写IT报障单寻求帮助。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载零信任工具，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问下载链接**  &#10;   根据您的操作系统，点击以下对应链接进行下载：&#10;   - **Windows版本**：[TrustCyberLink_PC_Setup_2.207.121.exe](https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe)（新版本）&#10;   - **Mac版本**：文档中未直接提供Mac安装包下载链接，但提到若需修复进程损坏可下载 `sdp_engine.exe`。如需完整Mac安装包，建议联系IT帮助台获取最新版本。&#10;&#10;2. **确认系统环境**  &#10;   - 如果您之前安装过“安全助手”，请先卸载（使用管理员口令 `e2vPsv8$`），再安装零信任工具。&#10;   - 如果没有安装过安全助手，可直接覆盖安装零信任工具。&#10;&#10;3. **开始安装**  &#10;   - 双击下载的安装包，按照提示完成安装（同意协议、选择安装路径等）。&#10;   - 安装完成后，桌面会出现零信任图标，打开后扫码登录即可使用。&#10;&#10;**💡 提示**: &#10;- 首次安装时若提示输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`。&#10;- 如遇安装或登录问题，请检查是否已正确卸载旧版软件或清除本地DNS设置（如 `127.0.0.1`）。&#10;&#10;如有其他问题随时问我！"/>
+        <filter val="好的!关于下载希沃传屏发送端安装包，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问希沃官网**  &#10;   打开浏览器，在地址栏输入 `www.baidu.com`，在搜索框中输入“希沃官网”并点击进入（请认准官方链接，避免进入错误网站）。&#10;&#10;2. **定位软件下载入口**  &#10;   在官网页面中，点击【服务支持】-【希沃软件】，向下滚动页面找到【希象传屏】，点击【立即下载】。&#10;&#10;3. **选择对应版本**  &#10;   在跳转后的页面中找到【希象传屏】，根据您的电脑系统选择对应的**发送端**版本进行下载：&#10;   - 如果是 Windows 系统，选择 Windows 版本；&#10;   - 如果是 Mac 系统，选择 Mac 版本。&#10;   *(注：接收端通常指一体机，需选择 Windows 版本；发送端即您的个人电脑)*&#10;&#10;4. **安装软件**  &#10;   下载完成后运行安装包。如果您的 C 盘空间不足，在安装过程中可选择其他磁盘分区进行安装。&#10;&#10;**💡 提示**: &#10;- 投屏前请确保发送端电脑与接收端（一体机）连接在**同一个 WiFi**网络下。&#10;- 如在使用过程中遇到其他问题，可联系 IT 帮助台或在 OA 上填写 IT 报障单（OA 系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
